--- a/docs/wo.xlsx
+++ b/docs/wo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\milne\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{327D0719-F897-487D-906D-750756189BD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{075C6216-AE42-450B-9E9C-E3A395EFD807}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{C32645C5-10AA-4D5C-BF11-217FF2F37ECD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{C32645C5-10AA-4D5C-BF11-217FF2F37ECD}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="215">
   <si>
     <t>Pause Barbell Lunge</t>
   </si>
@@ -633,9 +633,6 @@
     <t>KB Sumo Squat (40)</t>
   </si>
   <si>
-    <t>Halo</t>
-  </si>
-  <si>
     <t>Goblet Squat</t>
   </si>
   <si>
@@ -679,6 +676,12 @@
   </si>
   <si>
     <t>Ball Pike</t>
+  </si>
+  <si>
+    <t>Biceps</t>
+  </si>
+  <si>
+    <t>Rear Delt Raise</t>
   </si>
 </sst>
 </file>
@@ -694,12 +697,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -714,8 +723,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1622,9 +1632,6 @@
       <c r="F4" t="s">
         <v>20</v>
       </c>
-      <c r="H4" t="s">
-        <v>11</v>
-      </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
@@ -1645,12 +1652,6 @@
       <c r="F5" t="s">
         <v>121</v>
       </c>
-      <c r="G5" t="s">
-        <v>107</v>
-      </c>
-      <c r="H5" t="s">
-        <v>200</v>
-      </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
@@ -1671,12 +1672,6 @@
       <c r="F6" t="s">
         <v>48</v>
       </c>
-      <c r="G6" t="s">
-        <v>105</v>
-      </c>
-      <c r="H6" t="s">
-        <v>201</v>
-      </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
@@ -1697,12 +1692,6 @@
       <c r="F7" t="s">
         <v>52</v>
       </c>
-      <c r="G7" t="s">
-        <v>128</v>
-      </c>
-      <c r="H7" t="s">
-        <v>116</v>
-      </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
@@ -1723,12 +1712,6 @@
       <c r="F9" t="s">
         <v>123</v>
       </c>
-      <c r="G9" t="s">
-        <v>84</v>
-      </c>
-      <c r="H9" t="s">
-        <v>70</v>
-      </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
@@ -1743,12 +1726,6 @@
       <c r="F10" t="s">
         <v>9</v>
       </c>
-      <c r="G10" t="s">
-        <v>84</v>
-      </c>
-      <c r="H10" t="s">
-        <v>51</v>
-      </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
@@ -1777,12 +1754,6 @@
       <c r="B12" t="s">
         <v>81</v>
       </c>
-      <c r="G12" t="s">
-        <v>91</v>
-      </c>
-      <c r="H12" t="s">
-        <v>37</v>
-      </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
@@ -1797,12 +1768,6 @@
       <c r="F13" t="s">
         <v>28</v>
       </c>
-      <c r="G13" t="s">
-        <v>155</v>
-      </c>
-      <c r="H13" t="s">
-        <v>199</v>
-      </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
@@ -1837,12 +1802,6 @@
       <c r="F15" t="s">
         <v>122</v>
       </c>
-      <c r="G15" t="s">
-        <v>84</v>
-      </c>
-      <c r="H15" t="s">
-        <v>198</v>
-      </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
@@ -1851,14 +1810,8 @@
       <c r="B16" t="s">
         <v>96</v>
       </c>
-      <c r="G16" t="s">
-        <v>84</v>
-      </c>
-      <c r="H16" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>97</v>
       </c>
@@ -1878,7 +1831,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C18" t="s">
         <v>110</v>
       </c>
@@ -1891,14 +1844,8 @@
       <c r="F18" t="s">
         <v>125</v>
       </c>
-      <c r="G18" t="s">
-        <v>84</v>
-      </c>
-      <c r="H18" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>99</v>
       </c>
@@ -1911,14 +1858,8 @@
       <c r="F19" t="s">
         <v>126</v>
       </c>
-      <c r="G19" t="s">
-        <v>101</v>
-      </c>
-      <c r="H19" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>101</v>
       </c>
@@ -1931,14 +1872,8 @@
       <c r="D20" t="s">
         <v>120</v>
       </c>
-      <c r="G20" t="s">
-        <v>101</v>
-      </c>
-      <c r="H20" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>99</v>
       </c>
@@ -1946,7 +1881,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>129</v>
       </c>
@@ -1957,7 +1892,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>131</v>
       </c>
@@ -1977,7 +1912,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C26" t="s">
         <v>107</v>
       </c>
@@ -1991,7 +1926,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>133</v>
       </c>
@@ -2005,7 +1940,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>134</v>
       </c>
@@ -2019,7 +1954,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>135</v>
       </c>
@@ -2039,7 +1974,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C30" t="s">
         <v>93</v>
       </c>
@@ -2053,7 +1988,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>91</v>
       </c>
@@ -2061,7 +1996,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>138</v>
       </c>
@@ -2470,60 +2405,110 @@
         <v>179</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B65" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D65" t="s">
+        <v>11</v>
+      </c>
+      <c r="F65" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>99</v>
       </c>
       <c r="B66" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C66" t="s">
+        <v>107</v>
+      </c>
+      <c r="D66" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>99</v>
       </c>
       <c r="B67" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C67" t="s">
+        <v>105</v>
+      </c>
+      <c r="D67" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>101</v>
       </c>
       <c r="B68" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C68" t="s">
+        <v>128</v>
+      </c>
+      <c r="D68" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>194</v>
       </c>
       <c r="B70" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C70" t="s">
+        <v>84</v>
+      </c>
+      <c r="D70" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>189</v>
       </c>
       <c r="B71" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C71" t="s">
+        <v>84</v>
+      </c>
+      <c r="D71" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>93</v>
       </c>
       <c r="B73" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C73" t="s">
+        <v>91</v>
+      </c>
+      <c r="D73" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C74" t="s">
+        <v>155</v>
+      </c>
+      <c r="D74" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>101</v>
       </c>
@@ -2531,93 +2516,123 @@
         <v>191</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>101</v>
       </c>
       <c r="B76" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C76" t="s">
+        <v>84</v>
+      </c>
+      <c r="D76" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>84</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B77" s="1" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C77" t="s">
+        <v>84</v>
+      </c>
+      <c r="D77" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>91</v>
       </c>
       <c r="B79" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C79" t="s">
+        <v>84</v>
+      </c>
+      <c r="D79" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>155</v>
       </c>
       <c r="B80" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C80" t="s">
+        <v>101</v>
+      </c>
+      <c r="D80" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>91</v>
       </c>
       <c r="B81" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C81" t="s">
+        <v>101</v>
+      </c>
+      <c r="D81" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C86">
         <v>70</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
+        <v>203</v>
+      </c>
+      <c r="B87" t="s">
         <v>204</v>
       </c>
-      <c r="B87" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>105</v>
       </c>
       <c r="B88" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C88">
         <v>30</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>86</v>
       </c>
       <c r="B90" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>88</v>
       </c>
       <c r="B91" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>88</v>
       </c>
@@ -2625,18 +2640,18 @@
         <v>111</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>183</v>
       </c>
       <c r="B94" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C94">
         <v>55</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>183</v>
       </c>
@@ -2646,18 +2661,18 @@
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
+        <v>209</v>
+      </c>
+      <c r="B97" t="s">
         <v>210</v>
-      </c>
-      <c r="B97" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
+        <v>211</v>
+      </c>
+      <c r="B98" t="s">
         <v>212</v>
-      </c>
-      <c r="B98" t="s">
-        <v>213</v>
       </c>
     </row>
   </sheetData>

--- a/docs/wo.xlsx
+++ b/docs/wo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\milne\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{075C6216-AE42-450B-9E9C-E3A395EFD807}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BA20E64-562A-4C2B-9549-24BB5F2072F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{C32645C5-10AA-4D5C-BF11-217FF2F37ECD}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="246">
   <si>
     <t>Pause Barbell Lunge</t>
   </si>
@@ -645,43 +645,136 @@
     <t>Sit Up</t>
   </si>
   <si>
-    <t>DB RDL</t>
-  </si>
-  <si>
-    <t>4x11</t>
-  </si>
-  <si>
-    <t>Burpee</t>
-  </si>
-  <si>
-    <t>DB Lunge</t>
-  </si>
-  <si>
-    <t>WG Pull Up</t>
-  </si>
-  <si>
-    <t>Jump Squat</t>
-  </si>
-  <si>
-    <t>DB BOR</t>
-  </si>
-  <si>
-    <t>3x4</t>
-  </si>
-  <si>
-    <t>Ball Roll Out</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3x4 </t>
-  </si>
-  <si>
-    <t>Ball Pike</t>
-  </si>
-  <si>
-    <t>Biceps</t>
-  </si>
-  <si>
     <t>Rear Delt Raise</t>
+  </si>
+  <si>
+    <t>Biceps, Chest</t>
+  </si>
+  <si>
+    <t>DB Fly</t>
+  </si>
+  <si>
+    <t>Balance/ROM</t>
+  </si>
+  <si>
+    <t>Cable Kickback</t>
+  </si>
+  <si>
+    <t>Renegade Rows</t>
+  </si>
+  <si>
+    <t>DB RDL to BOR</t>
+  </si>
+  <si>
+    <t>Ball Back Hyperextension</t>
+  </si>
+  <si>
+    <t>Quads, Glutes, Shoulders</t>
+  </si>
+  <si>
+    <t>3x1min</t>
+  </si>
+  <si>
+    <t>DB Squat</t>
+  </si>
+  <si>
+    <t>DB Shoulder Press</t>
+  </si>
+  <si>
+    <t>Conc Curl</t>
+  </si>
+  <si>
+    <t>Clown Curl</t>
+  </si>
+  <si>
+    <t>Dec Push Up</t>
+  </si>
+  <si>
+    <t>Inc Bench</t>
+  </si>
+  <si>
+    <t>Pause Curl</t>
+  </si>
+  <si>
+    <t>Rev Crunch</t>
+  </si>
+  <si>
+    <t>Cable Kickbacks</t>
+  </si>
+  <si>
+    <t>Bench (DB, Alt DB)</t>
+  </si>
+  <si>
+    <t>Bird Dog Rows</t>
+  </si>
+  <si>
+    <t>DB Inc Press</t>
+  </si>
+  <si>
+    <t>Around the Worlds</t>
+  </si>
+  <si>
+    <t>Push Ups</t>
+  </si>
+  <si>
+    <t>Hammer Curl to Shoulder Press</t>
+  </si>
+  <si>
+    <t>BB Curl</t>
+  </si>
+  <si>
+    <t>Ball Crunch</t>
+  </si>
+  <si>
+    <t>Mtn Climbers</t>
+  </si>
+  <si>
+    <t>light weight; speed</t>
+  </si>
+  <si>
+    <t>Focus, good form</t>
+  </si>
+  <si>
+    <t>heavy major muscle group</t>
+  </si>
+  <si>
+    <t>Burnout, balance</t>
+  </si>
+  <si>
+    <t>Pendlay Row</t>
+  </si>
+  <si>
+    <t>Good Mornings</t>
+  </si>
+  <si>
+    <t>T Row</t>
+  </si>
+  <si>
+    <t>Yates Row</t>
+  </si>
+  <si>
+    <t>Ball Leg Curls</t>
+  </si>
+  <si>
+    <t>Band Kickbacks</t>
+  </si>
+  <si>
+    <t>DB Straight Leg DL</t>
+  </si>
+  <si>
+    <t>Quads, Triceps</t>
+  </si>
+  <si>
+    <t>Tricep Pushups</t>
+  </si>
+  <si>
+    <t>OH Walking Lunge</t>
+  </si>
+  <si>
+    <t>Tricep Extensions</t>
+  </si>
+  <si>
+    <t>Pause Front Squat</t>
   </si>
 </sst>
 </file>
@@ -1040,11 +1133,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F249B82-6886-4F60-BAAD-E01BA54A647B}">
-  <dimension ref="A1:C71"/>
+  <dimension ref="A1:C77"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="43.140625" customWidth="1"/>
-    <col min="2" max="2" width="11.7109375" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" customWidth="1"/>
     <col min="3" max="3" width="10.5703125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1200,17 +1293,14 @@
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>2</v>
-      </c>
-      <c r="B23" t="s">
-        <v>3</v>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="B24" t="s">
         <v>3</v>
@@ -1218,7 +1308,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="B25" t="s">
         <v>3</v>
@@ -1226,7 +1316,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B26" t="s">
         <v>3</v>
@@ -1234,23 +1324,23 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B27" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>24</v>
-      </c>
-      <c r="B29" t="s">
-        <v>25</v>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>58</v>
+      </c>
+      <c r="B28" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B30" t="s">
         <v>25</v>
@@ -1258,7 +1348,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>27</v>
+        <v>220</v>
       </c>
       <c r="B31" t="s">
         <v>25</v>
@@ -1266,7 +1356,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="B32" t="s">
         <v>25</v>
@@ -1274,31 +1364,31 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>47</v>
+      </c>
+      <c r="B33" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
         <v>81</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>6</v>
-      </c>
-      <c r="B35" t="s">
-        <v>7</v>
-      </c>
-      <c r="C35" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="B36" t="s">
         <v>7</v>
       </c>
+      <c r="C36" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B37" t="s">
         <v>7</v>
@@ -1306,7 +1396,7 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="B38" t="s">
         <v>7</v>
@@ -1314,7 +1404,7 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>49</v>
+        <v>221</v>
       </c>
       <c r="B39" t="s">
         <v>7</v>
@@ -1322,7 +1412,7 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B40" t="s">
         <v>7</v>
@@ -1330,7 +1420,7 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="B41" t="s">
         <v>7</v>
@@ -1338,31 +1428,28 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="B42" t="s">
         <v>7</v>
       </c>
     </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>73</v>
+      </c>
+      <c r="B43" t="s">
+        <v>7</v>
+      </c>
+    </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>9</v>
-      </c>
-      <c r="B44" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>37</v>
-      </c>
-      <c r="B45" t="s">
-        <v>10</v>
+        <v>182</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="B46" t="s">
         <v>10</v>
@@ -1370,18 +1457,15 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="B47" t="s">
         <v>10</v>
       </c>
-      <c r="C47" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="B48" t="s">
         <v>10</v>
@@ -1389,15 +1473,18 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="B49" t="s">
         <v>10</v>
       </c>
+      <c r="C49" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B50" t="s">
         <v>10</v>
@@ -1405,18 +1492,15 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="B51" t="s">
         <v>10</v>
       </c>
-      <c r="C51" t="s">
-        <v>1</v>
-      </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>79</v>
+        <v>53</v>
       </c>
       <c r="B52" t="s">
         <v>10</v>
@@ -1424,55 +1508,58 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="B53" t="s">
         <v>10</v>
       </c>
+      <c r="C53" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>79</v>
+      </c>
+      <c r="B54" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="B55" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>54</v>
-      </c>
-      <c r="B56" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="B57" t="s">
         <v>43</v>
       </c>
     </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>54</v>
+      </c>
+      <c r="B58" t="s">
+        <v>43</v>
+      </c>
+    </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>45</v>
-      </c>
-      <c r="B60" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="B61" t="s">
         <v>8</v>
@@ -1480,7 +1567,7 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="B62" t="s">
         <v>8</v>
@@ -1488,7 +1575,7 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B63" t="s">
         <v>8</v>
@@ -1496,7 +1583,7 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B64" t="s">
         <v>8</v>
@@ -1504,7 +1591,7 @@
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B65" t="s">
         <v>8</v>
@@ -1512,7 +1599,7 @@
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="B66" t="s">
         <v>8</v>
@@ -1520,34 +1607,60 @@
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="B67" t="s">
         <v>8</v>
       </c>
     </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>71</v>
+      </c>
+      <c r="B68" t="s">
+        <v>8</v>
+      </c>
+    </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B69" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>75</v>
-      </c>
-      <c r="B70" t="s">
-        <v>78</v>
+        <v>8</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B71" t="s">
         <v>78</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>75</v>
+      </c>
+      <c r="B72" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>76</v>
+      </c>
+      <c r="B73" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B77" t="s">
+        <v>205</v>
       </c>
     </row>
   </sheetData>
@@ -1557,7 +1670,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A791CA79-5EDF-4534-95D3-2767A2C8696F}">
-  <dimension ref="A2:S98"/>
+  <dimension ref="A2:S121"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.7109375" customWidth="1"/>
@@ -2413,7 +2526,7 @@
         <v>11</v>
       </c>
       <c r="F65" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -2429,6 +2542,12 @@
       <c r="D66" t="s">
         <v>199</v>
       </c>
+      <c r="E66" t="s">
+        <v>101</v>
+      </c>
+      <c r="F66" t="s">
+        <v>214</v>
+      </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
@@ -2443,6 +2562,12 @@
       <c r="D67" t="s">
         <v>200</v>
       </c>
+      <c r="E67" t="s">
+        <v>101</v>
+      </c>
+      <c r="F67" t="s">
+        <v>204</v>
+      </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
@@ -2457,6 +2582,12 @@
       <c r="D68" t="s">
         <v>116</v>
       </c>
+      <c r="E68" t="s">
+        <v>101</v>
+      </c>
+      <c r="F68" t="s">
+        <v>215</v>
+      </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
@@ -2471,6 +2602,12 @@
       <c r="D70" t="s">
         <v>70</v>
       </c>
+      <c r="E70" t="s">
+        <v>91</v>
+      </c>
+      <c r="F70" t="s">
+        <v>216</v>
+      </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
@@ -2485,6 +2622,20 @@
       <c r="D71" t="s">
         <v>51</v>
       </c>
+      <c r="E71" t="s">
+        <v>91</v>
+      </c>
+      <c r="F71" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E72" t="s">
+        <v>91</v>
+      </c>
+      <c r="F72" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
@@ -2507,6 +2658,12 @@
       <c r="D74" t="s">
         <v>198</v>
       </c>
+      <c r="E74" t="s">
+        <v>93</v>
+      </c>
+      <c r="F74" t="s">
+        <v>217</v>
+      </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
@@ -2529,6 +2686,12 @@
       <c r="D76" t="s">
         <v>52</v>
       </c>
+      <c r="E76" t="s">
+        <v>99</v>
+      </c>
+      <c r="F76" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
@@ -2541,7 +2704,13 @@
         <v>84</v>
       </c>
       <c r="D77" t="s">
-        <v>214</v>
+        <v>202</v>
+      </c>
+      <c r="E77" t="s">
+        <v>101</v>
+      </c>
+      <c r="F77" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -2556,6 +2725,12 @@
       </c>
       <c r="D79" t="s">
         <v>201</v>
+      </c>
+      <c r="E79" t="s">
+        <v>99</v>
+      </c>
+      <c r="F79" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -2571,8 +2746,14 @@
       <c r="D80" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E80" t="s">
+        <v>99</v>
+      </c>
+      <c r="F80" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>91</v>
       </c>
@@ -2585,94 +2766,441 @@
       <c r="D81" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E81" t="s">
+        <v>84</v>
+      </c>
+      <c r="F81" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B85" t="s">
+        <v>83</v>
+      </c>
+      <c r="D85" t="s">
+        <v>210</v>
+      </c>
+      <c r="F85" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>202</v>
-      </c>
-      <c r="C86">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+      <c r="C86" t="s">
+        <v>155</v>
+      </c>
+      <c r="D86" t="s">
+        <v>212</v>
+      </c>
+      <c r="E86" t="s">
+        <v>84</v>
+      </c>
+      <c r="F86" t="s">
+        <v>46</v>
+      </c>
+      <c r="H86" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>203</v>
+        <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+      <c r="C87" t="s">
+        <v>91</v>
+      </c>
+      <c r="D87" t="s">
+        <v>9</v>
+      </c>
+      <c r="E87" t="s">
+        <v>101</v>
+      </c>
+      <c r="F87" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="B88" t="s">
-        <v>205</v>
-      </c>
-      <c r="C88">
+        <v>208</v>
+      </c>
+      <c r="C88" t="s">
+        <v>155</v>
+      </c>
+      <c r="D88" t="s">
+        <v>154</v>
+      </c>
+      <c r="F88" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>84</v>
+      </c>
+      <c r="B90" t="s">
+        <v>90</v>
+      </c>
+      <c r="C90" t="s">
+        <v>91</v>
+      </c>
+      <c r="D90" t="s">
+        <v>111</v>
+      </c>
+      <c r="E90" t="s">
+        <v>91</v>
+      </c>
+      <c r="F90" t="s">
+        <v>223</v>
+      </c>
+      <c r="H90" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C91" t="s">
+        <v>91</v>
+      </c>
+      <c r="D91" t="s">
+        <v>112</v>
+      </c>
+      <c r="E91" t="s">
+        <v>91</v>
+      </c>
+      <c r="F91" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>91</v>
+      </c>
+      <c r="B92" t="s">
+        <v>92</v>
+      </c>
+      <c r="C92" t="s">
+        <v>91</v>
+      </c>
+      <c r="D92" t="s">
+        <v>53</v>
+      </c>
+      <c r="E92" t="s">
+        <v>155</v>
+      </c>
+      <c r="F92" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>91</v>
+      </c>
+      <c r="B93" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C94" t="s">
+        <v>114</v>
+      </c>
+      <c r="D94" t="s">
+        <v>115</v>
+      </c>
+      <c r="E94" t="s">
+        <v>93</v>
+      </c>
+      <c r="F94" t="s">
+        <v>48</v>
+      </c>
+      <c r="H94" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>93</v>
+      </c>
+      <c r="B95" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
-        <v>86</v>
-      </c>
-      <c r="B90" t="s">
+      <c r="C95" t="s">
+        <v>91</v>
+      </c>
+      <c r="D95" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C96" t="s">
+        <v>91</v>
+      </c>
+      <c r="D96" t="s">
+        <v>67</v>
+      </c>
+      <c r="E96" t="s">
+        <v>84</v>
+      </c>
+      <c r="F96" t="s">
+        <v>28</v>
+      </c>
+      <c r="H96" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>101</v>
+      </c>
+      <c r="B97" t="s">
+        <v>207</v>
+      </c>
+      <c r="E97" t="s">
+        <v>99</v>
+      </c>
+      <c r="F97" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>101</v>
+      </c>
+      <c r="B98" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
-        <v>88</v>
-      </c>
-      <c r="B91" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
-        <v>88</v>
-      </c>
-      <c r="B92" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
-        <v>183</v>
-      </c>
-      <c r="B94" t="s">
-        <v>208</v>
-      </c>
-      <c r="C94">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
-        <v>183</v>
-      </c>
-      <c r="B95" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
+      <c r="C98" t="s">
+        <v>155</v>
+      </c>
+      <c r="D98" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E99" t="s">
+        <v>168</v>
+      </c>
+      <c r="F99" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>91</v>
+      </c>
+      <c r="B100" t="s">
+        <v>102</v>
+      </c>
+      <c r="C100" t="s">
+        <v>211</v>
+      </c>
+      <c r="D100" t="s">
+        <v>61</v>
+      </c>
+      <c r="E100" t="s">
+        <v>168</v>
+      </c>
+      <c r="F100" t="s">
         <v>209</v>
       </c>
-      <c r="B97" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
-        <v>211</v>
-      </c>
-      <c r="B98" t="s">
-        <v>212</v>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>91</v>
+      </c>
+      <c r="B101" t="s">
+        <v>209</v>
+      </c>
+      <c r="C101" t="s">
+        <v>99</v>
+      </c>
+      <c r="D101" t="s">
+        <v>150</v>
+      </c>
+      <c r="E101" t="s">
+        <v>168</v>
+      </c>
+      <c r="F101" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B105" t="s">
+        <v>187</v>
+      </c>
+      <c r="D105" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>99</v>
+      </c>
+      <c r="B106" t="s">
+        <v>235</v>
+      </c>
+      <c r="C106" t="s">
+        <v>101</v>
+      </c>
+      <c r="D106" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>99</v>
+      </c>
+      <c r="B107" t="s">
+        <v>154</v>
+      </c>
+      <c r="C107" t="s">
+        <v>101</v>
+      </c>
+      <c r="D107" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>101</v>
+      </c>
+      <c r="B108" t="s">
+        <v>236</v>
+      </c>
+      <c r="C108" t="s">
+        <v>101</v>
+      </c>
+      <c r="D108" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>91</v>
+      </c>
+      <c r="B110" t="s">
+        <v>63</v>
+      </c>
+      <c r="C110" t="s">
+        <v>91</v>
+      </c>
+      <c r="D110" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>91</v>
+      </c>
+      <c r="B111" t="s">
+        <v>240</v>
+      </c>
+      <c r="C111" t="s">
+        <v>91</v>
+      </c>
+      <c r="D111" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>91</v>
+      </c>
+      <c r="B112" t="s">
+        <v>237</v>
+      </c>
+      <c r="C112" t="s">
+        <v>91</v>
+      </c>
+      <c r="D112" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>93</v>
+      </c>
+      <c r="B114" t="s">
+        <v>234</v>
+      </c>
+      <c r="C114" t="s">
+        <v>93</v>
+      </c>
+      <c r="D114" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>99</v>
+      </c>
+      <c r="B116" t="s">
+        <v>239</v>
+      </c>
+      <c r="C116" t="s">
+        <v>101</v>
+      </c>
+      <c r="D116" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>99</v>
+      </c>
+      <c r="B117" t="s">
+        <v>238</v>
+      </c>
+      <c r="C117" t="s">
+        <v>99</v>
+      </c>
+      <c r="D117" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>101</v>
+      </c>
+      <c r="B119" t="s">
+        <v>45</v>
+      </c>
+      <c r="C119" t="s">
+        <v>99</v>
+      </c>
+      <c r="D119" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>99</v>
+      </c>
+      <c r="B120" t="s">
+        <v>44</v>
+      </c>
+      <c r="C120" t="s">
+        <v>99</v>
+      </c>
+      <c r="D120" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C121" t="s">
+        <v>99</v>
+      </c>
+      <c r="D121" t="s">
+        <v>163</v>
       </c>
     </row>
   </sheetData>

--- a/docs/wo.xlsx
+++ b/docs/wo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\milne\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\milne\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BA20E64-562A-4C2B-9549-24BB5F2072F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{252511F1-DB7C-4F5A-8347-F9DFFE3A150D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{C32645C5-10AA-4D5C-BF11-217FF2F37ECD}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="742" uniqueCount="285">
   <si>
     <t>Pause Barbell Lunge</t>
   </si>
@@ -775,6 +775,123 @@
   </si>
   <si>
     <t>Pause Front Squat</t>
+  </si>
+  <si>
+    <t>Hamstring Curls</t>
+  </si>
+  <si>
+    <t>Leg Press</t>
+  </si>
+  <si>
+    <t>T Push Up</t>
+  </si>
+  <si>
+    <t>Alt. DB Bench</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sit up </t>
+  </si>
+  <si>
+    <t>Weighted Ball Hyperext</t>
+  </si>
+  <si>
+    <t>Hamstrings, Biceps</t>
+  </si>
+  <si>
+    <t>Hamstring Curl</t>
+  </si>
+  <si>
+    <t>Back, Quads, Glutes</t>
+  </si>
+  <si>
+    <t>Conc. Curl</t>
+  </si>
+  <si>
+    <t>Elevated DL</t>
+  </si>
+  <si>
+    <t>Inc. Bench Curl</t>
+  </si>
+  <si>
+    <t>BB RDL</t>
+  </si>
+  <si>
+    <t>Single Leg RDL</t>
+  </si>
+  <si>
+    <t>Bulg Split Squat</t>
+  </si>
+  <si>
+    <t>KB Swings</t>
+  </si>
+  <si>
+    <t>Lunges</t>
+  </si>
+  <si>
+    <t>Squats</t>
+  </si>
+  <si>
+    <t>Dec. Push Ups</t>
+  </si>
+  <si>
+    <t>Kneeling Landmine Press</t>
+  </si>
+  <si>
+    <t>DB Bench</t>
+  </si>
+  <si>
+    <t>Rev. Crunch</t>
+  </si>
+  <si>
+    <t>Ball Back Ext</t>
+  </si>
+  <si>
+    <t>Hamstrings, Shoulders</t>
+  </si>
+  <si>
+    <t>Half Kneeling bottoms up KB Press</t>
+  </si>
+  <si>
+    <t>Seated Lat Raise</t>
+  </si>
+  <si>
+    <t>Push Press</t>
+  </si>
+  <si>
+    <t>Quads, Glutes, Biceps</t>
+  </si>
+  <si>
+    <t>Leg Extension</t>
+  </si>
+  <si>
+    <t>Goblet Squats</t>
+  </si>
+  <si>
+    <t>Step Ups</t>
+  </si>
+  <si>
+    <t>21s</t>
+  </si>
+  <si>
+    <t>3x21</t>
+  </si>
+  <si>
+    <t>Chest, Back</t>
+  </si>
+  <si>
+    <t>Landmine Row</t>
+  </si>
+  <si>
+    <t>Alt DB Bench</t>
+  </si>
+  <si>
+    <t>Yates Row (underhand)</t>
+  </si>
+  <si>
+    <t>Inc DB Bench</t>
+  </si>
+  <si>
+    <t>Hamstrings, Triceps</t>
   </si>
 </sst>
 </file>
@@ -1133,7 +1250,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F249B82-6886-4F60-BAAD-E01BA54A647B}">
-  <dimension ref="A1:C77"/>
+  <dimension ref="A1:C80"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="43.140625" customWidth="1"/>
@@ -1197,17 +1314,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>30</v>
-      </c>
-      <c r="B9" t="s">
-        <v>31</v>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>247</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B10" t="s">
         <v>31</v>
@@ -1215,7 +1332,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B11" t="s">
         <v>31</v>
@@ -1223,7 +1340,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B12" t="s">
         <v>31</v>
@@ -1231,7 +1348,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B13" t="s">
         <v>31</v>
@@ -1239,31 +1356,31 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B14" t="s">
         <v>31</v>
       </c>
     </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15" t="s">
+        <v>31</v>
+      </c>
+    </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>16</v>
+        <v>246</v>
       </c>
       <c r="B16" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B18" t="s">
         <v>17</v>
@@ -1271,7 +1388,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="B19" t="s">
         <v>17</v>
@@ -1279,7 +1396,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>63</v>
+        <v>19</v>
       </c>
       <c r="B20" t="s">
         <v>17</v>
@@ -1287,7 +1404,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="B21" t="s">
         <v>17</v>
@@ -1295,36 +1412,33 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>222</v>
+        <v>63</v>
+      </c>
+      <c r="B22" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>64</v>
+      </c>
+      <c r="B23" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>2</v>
-      </c>
-      <c r="B24" t="s">
-        <v>3</v>
+        <v>222</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>40</v>
-      </c>
-      <c r="B25" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>55</v>
-      </c>
-      <c r="B26" t="s">
-        <v>3</v>
+        <v>282</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="B27" t="s">
         <v>3</v>
@@ -1332,39 +1446,39 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="B28" t="s">
         <v>3</v>
       </c>
     </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>55</v>
+      </c>
+      <c r="B29" t="s">
+        <v>3</v>
+      </c>
+    </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="B30" t="s">
-        <v>25</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>220</v>
+        <v>58</v>
       </c>
       <c r="B31" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>27</v>
-      </c>
-      <c r="B32" t="s">
-        <v>25</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="B33" t="s">
         <v>25</v>
@@ -1372,47 +1486,47 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>81</v>
+        <v>220</v>
+      </c>
+      <c r="B34" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>27</v>
+      </c>
+      <c r="B35" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="B36" t="s">
-        <v>7</v>
-      </c>
-      <c r="C36" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>35</v>
-      </c>
-      <c r="B37" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>36</v>
-      </c>
-      <c r="B38" t="s">
-        <v>7</v>
+        <v>81</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>221</v>
+        <v>6</v>
       </c>
       <c r="B39" t="s">
         <v>7</v>
       </c>
+      <c r="C39" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="B40" t="s">
         <v>7</v>
@@ -1420,7 +1534,7 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="B41" t="s">
         <v>7</v>
@@ -1428,7 +1542,7 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>62</v>
+        <v>221</v>
       </c>
       <c r="B42" t="s">
         <v>7</v>
@@ -1436,7 +1550,7 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="B43" t="s">
         <v>7</v>
@@ -1444,47 +1558,44 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>182</v>
+        <v>50</v>
+      </c>
+      <c r="B44" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>62</v>
+      </c>
+      <c r="B45" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>9</v>
+        <v>73</v>
       </c>
       <c r="B46" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>37</v>
-      </c>
-      <c r="B47" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>38</v>
-      </c>
-      <c r="B48" t="s">
-        <v>10</v>
+        <v>182</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="B49" t="s">
         <v>10</v>
       </c>
-      <c r="C49" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="B50" t="s">
         <v>10</v>
@@ -1492,7 +1603,7 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="B51" t="s">
         <v>10</v>
@@ -1500,26 +1611,26 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="B52" t="s">
         <v>10</v>
       </c>
+      <c r="C52" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="B53" t="s">
         <v>10</v>
       </c>
-      <c r="C53" t="s">
-        <v>1</v>
-      </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>79</v>
+        <v>52</v>
       </c>
       <c r="B54" t="s">
         <v>10</v>
@@ -1527,63 +1638,66 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>80</v>
+        <v>53</v>
       </c>
       <c r="B55" t="s">
         <v>10</v>
       </c>
     </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>70</v>
+      </c>
+      <c r="B56" t="s">
+        <v>10</v>
+      </c>
+      <c r="C56" t="s">
+        <v>1</v>
+      </c>
+    </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>42</v>
+        <v>79</v>
       </c>
       <c r="B57" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="B58" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>57</v>
-      </c>
-      <c r="B59" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>42</v>
+      </c>
+      <c r="B60" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="B61" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="B62" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>59</v>
-      </c>
-      <c r="B63" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="B64" t="s">
         <v>8</v>
@@ -1591,7 +1705,7 @@
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="B65" t="s">
         <v>8</v>
@@ -1599,7 +1713,7 @@
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B66" t="s">
         <v>8</v>
@@ -1607,7 +1721,7 @@
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="B67" t="s">
         <v>8</v>
@@ -1615,7 +1729,7 @@
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="B68" t="s">
         <v>8</v>
@@ -1623,43 +1737,67 @@
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="B69" t="s">
         <v>8</v>
       </c>
     </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>66</v>
+      </c>
+      <c r="B70" t="s">
+        <v>8</v>
+      </c>
+    </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B71" t="s">
-        <v>78</v>
+        <v>8</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B72" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>76</v>
-      </c>
-      <c r="B73" t="s">
-        <v>78</v>
+        <v>8</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
+        <v>74</v>
+      </c>
+      <c r="B74" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>75</v>
+      </c>
+      <c r="B75" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>76</v>
+      </c>
+      <c r="B76" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B77" t="s">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B80" t="s">
         <v>205</v>
       </c>
     </row>
@@ -1670,7 +1808,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A791CA79-5EDF-4534-95D3-2767A2C8696F}">
-  <dimension ref="A2:S121"/>
+  <dimension ref="A2:S161"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.7109375" customWidth="1"/>
@@ -2697,7 +2835,7 @@
       <c r="A77" t="s">
         <v>84</v>
       </c>
-      <c r="B77" s="1" t="s">
+      <c r="B77" t="s">
         <v>195</v>
       </c>
       <c r="C77" t="s">
@@ -3040,6 +3178,9 @@
       <c r="D105" t="s">
         <v>241</v>
       </c>
+      <c r="F105" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
@@ -3054,6 +3195,12 @@
       <c r="D106" t="s">
         <v>244</v>
       </c>
+      <c r="E106" t="s">
+        <v>101</v>
+      </c>
+      <c r="F106" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
@@ -3068,6 +3215,12 @@
       <c r="D107" t="s">
         <v>68</v>
       </c>
+      <c r="E107" t="s">
+        <v>101</v>
+      </c>
+      <c r="F107" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
@@ -3082,6 +3235,12 @@
       <c r="D108" t="s">
         <v>242</v>
       </c>
+      <c r="E108" t="s">
+        <v>99</v>
+      </c>
+      <c r="F108" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
@@ -3096,6 +3255,12 @@
       <c r="D110" t="s">
         <v>198</v>
       </c>
+      <c r="E110" t="s">
+        <v>155</v>
+      </c>
+      <c r="F110" t="s">
+        <v>249</v>
+      </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
@@ -3110,6 +3275,12 @@
       <c r="D111" t="s">
         <v>27</v>
       </c>
+      <c r="E111" t="s">
+        <v>91</v>
+      </c>
+      <c r="F111" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
@@ -3119,13 +3290,19 @@
         <v>237</v>
       </c>
       <c r="C112" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="D112" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E112" t="s">
+        <v>155</v>
+      </c>
+      <c r="F112" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>93</v>
       </c>
@@ -3138,8 +3315,14 @@
       <c r="D114" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E114" t="s">
+        <v>93</v>
+      </c>
+      <c r="F114" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>99</v>
       </c>
@@ -3152,8 +3335,14 @@
       <c r="D116" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E116" t="s">
+        <v>101</v>
+      </c>
+      <c r="F116" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>99</v>
       </c>
@@ -3166,8 +3355,14 @@
       <c r="D117" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E117" t="s">
+        <v>84</v>
+      </c>
+      <c r="F117" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>101</v>
       </c>
@@ -3180,8 +3375,14 @@
       <c r="D119" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E119" t="s">
+        <v>101</v>
+      </c>
+      <c r="F119" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>99</v>
       </c>
@@ -3194,13 +3395,520 @@
       <c r="D120" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E120" t="s">
+        <v>101</v>
+      </c>
+      <c r="F120" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C121" t="s">
         <v>99</v>
       </c>
       <c r="D121" t="s">
         <v>163</v>
+      </c>
+      <c r="E121" t="s">
+        <v>127</v>
+      </c>
+      <c r="F121" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B124" t="s">
+        <v>252</v>
+      </c>
+      <c r="D124" t="s">
+        <v>254</v>
+      </c>
+      <c r="F124" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>101</v>
+      </c>
+      <c r="B125" t="s">
+        <v>255</v>
+      </c>
+      <c r="C125" t="s">
+        <v>101</v>
+      </c>
+      <c r="D125" t="s">
+        <v>260</v>
+      </c>
+      <c r="E125" t="s">
+        <v>101</v>
+      </c>
+      <c r="F125" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>101</v>
+      </c>
+      <c r="B126" t="s">
+        <v>39</v>
+      </c>
+      <c r="C126" t="s">
+        <v>101</v>
+      </c>
+      <c r="D126" t="s">
+        <v>222</v>
+      </c>
+      <c r="E126" t="s">
+        <v>101</v>
+      </c>
+      <c r="F126" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>99</v>
+      </c>
+      <c r="B127" t="s">
+        <v>171</v>
+      </c>
+      <c r="C127" t="s">
+        <v>211</v>
+      </c>
+      <c r="D127" t="s">
+        <v>190</v>
+      </c>
+      <c r="E127" t="s">
+        <v>101</v>
+      </c>
+      <c r="F127" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>91</v>
+      </c>
+      <c r="B129" t="s">
+        <v>253</v>
+      </c>
+      <c r="C129" t="s">
+        <v>91</v>
+      </c>
+      <c r="D129" t="s">
+        <v>263</v>
+      </c>
+      <c r="E129" t="s">
+        <v>91</v>
+      </c>
+      <c r="F129" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>155</v>
+      </c>
+      <c r="B130" t="s">
+        <v>257</v>
+      </c>
+      <c r="C130" t="s">
+        <v>91</v>
+      </c>
+      <c r="D130" t="s">
+        <v>19</v>
+      </c>
+      <c r="E130" t="s">
+        <v>91</v>
+      </c>
+      <c r="F130" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>91</v>
+      </c>
+      <c r="B131" t="s">
+        <v>258</v>
+      </c>
+      <c r="C131" t="s">
+        <v>91</v>
+      </c>
+      <c r="D131" t="s">
+        <v>262</v>
+      </c>
+      <c r="E131" t="s">
+        <v>91</v>
+      </c>
+      <c r="F131" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>101</v>
+      </c>
+      <c r="B133" t="s">
+        <v>256</v>
+      </c>
+      <c r="C133" t="s">
+        <v>93</v>
+      </c>
+      <c r="D133" t="s">
+        <v>274</v>
+      </c>
+      <c r="E133" t="s">
+        <v>93</v>
+      </c>
+      <c r="F133" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>101</v>
+      </c>
+      <c r="B134" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>101</v>
+      </c>
+      <c r="B135" t="s">
+        <v>259</v>
+      </c>
+      <c r="C135" t="s">
+        <v>101</v>
+      </c>
+      <c r="D135" t="s">
+        <v>156</v>
+      </c>
+      <c r="E135" t="s">
+        <v>99</v>
+      </c>
+      <c r="F135" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C136" t="s">
+        <v>99</v>
+      </c>
+      <c r="D136" t="s">
+        <v>261</v>
+      </c>
+      <c r="E136" t="s">
+        <v>84</v>
+      </c>
+      <c r="F136" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>101</v>
+      </c>
+      <c r="B137" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>101</v>
+      </c>
+      <c r="B138" t="s">
+        <v>124</v>
+      </c>
+      <c r="C138" t="s">
+        <v>101</v>
+      </c>
+      <c r="D138" t="s">
+        <v>45</v>
+      </c>
+      <c r="E138" t="s">
+        <v>99</v>
+      </c>
+      <c r="F138" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>168</v>
+      </c>
+      <c r="B139" t="s">
+        <v>228</v>
+      </c>
+      <c r="C139" t="s">
+        <v>99</v>
+      </c>
+      <c r="D139" t="s">
+        <v>44</v>
+      </c>
+      <c r="E139" t="s">
+        <v>99</v>
+      </c>
+      <c r="F139" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B142" t="s">
+        <v>269</v>
+      </c>
+      <c r="D142" t="s">
+        <v>273</v>
+      </c>
+      <c r="F142" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>101</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="C143" t="s">
+        <v>101</v>
+      </c>
+      <c r="D143" t="s">
+        <v>227</v>
+      </c>
+      <c r="E143" t="s">
+        <v>99</v>
+      </c>
+      <c r="F143" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>101</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="C144" t="s">
+        <v>101</v>
+      </c>
+      <c r="D144" t="s">
+        <v>275</v>
+      </c>
+      <c r="E144" t="s">
+        <v>99</v>
+      </c>
+      <c r="F144" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>101</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C145" t="s">
+        <v>99</v>
+      </c>
+      <c r="D145" t="s">
+        <v>239</v>
+      </c>
+      <c r="E145" t="s">
+        <v>99</v>
+      </c>
+      <c r="F145" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>91</v>
+      </c>
+      <c r="B147" t="s">
+        <v>9</v>
+      </c>
+      <c r="C147" t="s">
+        <v>91</v>
+      </c>
+      <c r="D147" t="s">
+        <v>274</v>
+      </c>
+      <c r="E147" t="s">
+        <v>91</v>
+      </c>
+      <c r="F147" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>91</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C148" t="s">
+        <v>155</v>
+      </c>
+      <c r="D148" t="s">
+        <v>55</v>
+      </c>
+      <c r="E148" t="s">
+        <v>91</v>
+      </c>
+      <c r="F148" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>91</v>
+      </c>
+      <c r="B149" t="s">
+        <v>161</v>
+      </c>
+      <c r="C149" t="s">
+        <v>114</v>
+      </c>
+      <c r="D149" t="s">
+        <v>115</v>
+      </c>
+      <c r="E149" t="s">
+        <v>155</v>
+      </c>
+      <c r="F149" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>93</v>
+      </c>
+      <c r="B151" t="s">
+        <v>246</v>
+      </c>
+      <c r="C151" t="s">
+        <v>278</v>
+      </c>
+      <c r="D151" t="s">
+        <v>277</v>
+      </c>
+      <c r="E151" t="s">
+        <v>93</v>
+      </c>
+      <c r="F151" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C152" t="s">
+        <v>101</v>
+      </c>
+      <c r="D152" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>99</v>
+      </c>
+      <c r="B153" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="C153" t="s">
+        <v>99</v>
+      </c>
+      <c r="D153" t="s">
+        <v>159</v>
+      </c>
+      <c r="E153" t="s">
+        <v>99</v>
+      </c>
+      <c r="F153" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>99</v>
+      </c>
+      <c r="B154" t="s">
+        <v>272</v>
+      </c>
+      <c r="E154" t="s">
+        <v>84</v>
+      </c>
+      <c r="F154" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C155" t="s">
+        <v>211</v>
+      </c>
+      <c r="D155" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>168</v>
+      </c>
+      <c r="B156" t="s">
+        <v>228</v>
+      </c>
+      <c r="C156" t="s">
+        <v>99</v>
+      </c>
+      <c r="D156" t="s">
+        <v>150</v>
+      </c>
+      <c r="E156" t="s">
+        <v>84</v>
+      </c>
+      <c r="F156" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>166</v>
+      </c>
+      <c r="B157" t="s">
+        <v>180</v>
+      </c>
+      <c r="E157" t="s">
+        <v>99</v>
+      </c>
+      <c r="F157" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>99</v>
+      </c>
+      <c r="B158" t="s">
+        <v>163</v>
+      </c>
+      <c r="E158" t="s">
+        <v>101</v>
+      </c>
+      <c r="F158" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="161" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B161" t="s">
+        <v>284</v>
       </c>
     </row>
   </sheetData>

--- a/docs/wo.xlsx
+++ b/docs/wo.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\milne\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nmilner\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{252511F1-DB7C-4F5A-8347-F9DFFE3A150D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{358B75AF-7BB6-4BE3-936A-700DF72AFD3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{C32645C5-10AA-4D5C-BF11-217FF2F37ECD}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{C32645C5-10AA-4D5C-BF11-217FF2F37ECD}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="742" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="789" uniqueCount="291">
   <si>
     <t>Pause Barbell Lunge</t>
   </si>
@@ -852,9 +852,6 @@
     <t>Half Kneeling bottoms up KB Press</t>
   </si>
   <si>
-    <t>Seated Lat Raise</t>
-  </si>
-  <si>
     <t>Push Press</t>
   </si>
   <si>
@@ -892,6 +889,27 @@
   </si>
   <si>
     <t>Hamstrings, Triceps</t>
+  </si>
+  <si>
+    <t>Seated Tri Ext</t>
+  </si>
+  <si>
+    <t>Alt One Arm KB Swing</t>
+  </si>
+  <si>
+    <t>DB Elevated DL</t>
+  </si>
+  <si>
+    <t>Quads, Shoulders, Glutes</t>
+  </si>
+  <si>
+    <t>One Arm DB Shoulder Press</t>
+  </si>
+  <si>
+    <t>Seated Lateral Raise</t>
+  </si>
+  <si>
+    <t>Landmine Reverse Lunge</t>
   </si>
 </sst>
 </file>
@@ -907,18 +925,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -933,9 +945,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1433,7 +1444,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -1808,7 +1819,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A791CA79-5EDF-4534-95D3-2767A2C8696F}">
-  <dimension ref="A2:S161"/>
+  <dimension ref="A2:S177"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.7109375" customWidth="1"/>
@@ -3558,7 +3569,7 @@
         <v>93</v>
       </c>
       <c r="D133" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E133" t="s">
         <v>93</v>
@@ -3662,17 +3673,17 @@
         <v>269</v>
       </c>
       <c r="D142" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F142" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>101</v>
       </c>
-      <c r="B143" s="1" t="s">
+      <c r="B143" t="s">
         <v>235</v>
       </c>
       <c r="C143" t="s">
@@ -3685,21 +3696,21 @@
         <v>99</v>
       </c>
       <c r="F143" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>101</v>
       </c>
-      <c r="B144" s="1" t="s">
+      <c r="B144" t="s">
         <v>270</v>
       </c>
       <c r="C144" t="s">
         <v>101</v>
       </c>
       <c r="D144" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E144" t="s">
         <v>99</v>
@@ -3712,7 +3723,7 @@
       <c r="A145" t="s">
         <v>101</v>
       </c>
-      <c r="B145" s="1" t="s">
+      <c r="B145" t="s">
         <v>33</v>
       </c>
       <c r="C145" t="s">
@@ -3725,7 +3736,7 @@
         <v>99</v>
       </c>
       <c r="F145" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
@@ -3739,7 +3750,7 @@
         <v>91</v>
       </c>
       <c r="D147" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E147" t="s">
         <v>91</v>
@@ -3752,7 +3763,7 @@
       <c r="A148" t="s">
         <v>91</v>
       </c>
-      <c r="B148" s="1" t="s">
+      <c r="B148" t="s">
         <v>30</v>
       </c>
       <c r="C148" t="s">
@@ -3796,16 +3807,16 @@
         <v>246</v>
       </c>
       <c r="C151" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D151" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E151" t="s">
         <v>93</v>
       </c>
       <c r="F151" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
@@ -3813,15 +3824,15 @@
         <v>101</v>
       </c>
       <c r="D152" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>99</v>
       </c>
-      <c r="B153" s="1" t="s">
-        <v>271</v>
+      <c r="B153" t="s">
+        <v>289</v>
       </c>
       <c r="C153" t="s">
         <v>99</v>
@@ -3841,7 +3852,7 @@
         <v>99</v>
       </c>
       <c r="B154" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E154" t="s">
         <v>84</v>
@@ -3906,9 +3917,174 @@
         <v>60</v>
       </c>
     </row>
-    <row r="161" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B161" t="s">
+        <v>283</v>
+      </c>
+      <c r="D161" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>101</v>
+      </c>
+      <c r="B162" t="s">
+        <v>182</v>
+      </c>
+      <c r="C162" t="s">
+        <v>101</v>
+      </c>
+      <c r="D162" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>101</v>
+      </c>
+      <c r="B163" t="s">
+        <v>286</v>
+      </c>
+      <c r="C163" t="s">
+        <v>101</v>
+      </c>
+      <c r="D163" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>84</v>
+      </c>
+      <c r="B164" t="s">
+        <v>285</v>
+      </c>
+      <c r="C164" t="s">
+        <v>101</v>
+      </c>
+      <c r="D164" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>91</v>
+      </c>
+      <c r="B166" t="s">
         <v>284</v>
+      </c>
+      <c r="C166" t="s">
+        <v>91</v>
+      </c>
+      <c r="D166" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>91</v>
+      </c>
+      <c r="B167" t="s">
+        <v>258</v>
+      </c>
+      <c r="C167" t="s">
+        <v>91</v>
+      </c>
+      <c r="D167" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>91</v>
+      </c>
+      <c r="B168" t="s">
+        <v>27</v>
+      </c>
+      <c r="C168" t="s">
+        <v>91</v>
+      </c>
+      <c r="D168" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>93</v>
+      </c>
+      <c r="B170" t="s">
+        <v>30</v>
+      </c>
+      <c r="C170" t="s">
+        <v>93</v>
+      </c>
+      <c r="D170" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>101</v>
+      </c>
+      <c r="B172" t="s">
+        <v>39</v>
+      </c>
+      <c r="C172" t="s">
+        <v>101</v>
+      </c>
+      <c r="D172" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>99</v>
+      </c>
+      <c r="B173" t="s">
+        <v>157</v>
+      </c>
+      <c r="C173" t="s">
+        <v>101</v>
+      </c>
+      <c r="D173" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>99</v>
+      </c>
+      <c r="B175" t="s">
+        <v>163</v>
+      </c>
+      <c r="C175" t="s">
+        <v>101</v>
+      </c>
+      <c r="D175" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>166</v>
+      </c>
+      <c r="B176" t="s">
+        <v>165</v>
+      </c>
+      <c r="C176" t="s">
+        <v>99</v>
+      </c>
+      <c r="D176" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>166</v>
+      </c>
+      <c r="B177" t="s">
+        <v>164</v>
       </c>
     </row>
   </sheetData>

--- a/docs/wo.xlsx
+++ b/docs/wo.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nmilner\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\milne\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{358B75AF-7BB6-4BE3-936A-700DF72AFD3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{137BD0D5-DD3E-4AD2-9DF5-1498CEA1CB33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{C32645C5-10AA-4D5C-BF11-217FF2F37ECD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{C32645C5-10AA-4D5C-BF11-217FF2F37ECD}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="789" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="837" uniqueCount="295">
   <si>
     <t>Pause Barbell Lunge</t>
   </si>
@@ -910,6 +910,18 @@
   </si>
   <si>
     <t>Landmine Reverse Lunge</t>
+  </si>
+  <si>
+    <t>Dec Push Ups</t>
+  </si>
+  <si>
+    <t>Back, Hamstrings</t>
+  </si>
+  <si>
+    <t>DB Sing Leg RDL</t>
+  </si>
+  <si>
+    <t>RDL to Row</t>
   </si>
 </sst>
 </file>
@@ -945,8 +957,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1819,7 +1832,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A791CA79-5EDF-4534-95D3-2767A2C8696F}">
-  <dimension ref="A2:S177"/>
+  <dimension ref="A2:S195"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.7109375" customWidth="1"/>
@@ -3917,15 +3930,18 @@
         <v>60</v>
       </c>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B161" t="s">
         <v>283</v>
       </c>
       <c r="D161" t="s">
         <v>287</v>
       </c>
-    </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F161" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>101</v>
       </c>
@@ -3938,8 +3954,14 @@
       <c r="D162" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E162" t="s">
+        <v>84</v>
+      </c>
+      <c r="F162" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>101</v>
       </c>
@@ -3952,8 +3974,14 @@
       <c r="D163" t="s">
         <v>290</v>
       </c>
-    </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E163" t="s">
+        <v>101</v>
+      </c>
+      <c r="F163" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>84</v>
       </c>
@@ -3966,8 +3994,14 @@
       <c r="D164" t="s">
         <v>288</v>
       </c>
-    </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E164" t="s">
+        <v>99</v>
+      </c>
+      <c r="F164" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>91</v>
       </c>
@@ -3980,8 +4014,14 @@
       <c r="D166" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E166" t="s">
+        <v>91</v>
+      </c>
+      <c r="F166" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>91</v>
       </c>
@@ -3994,8 +4034,14 @@
       <c r="D167" t="s">
         <v>260</v>
       </c>
-    </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E167" t="s">
+        <v>91</v>
+      </c>
+      <c r="F167" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>91</v>
       </c>
@@ -4008,8 +4054,14 @@
       <c r="D168" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E168" t="s">
+        <v>155</v>
+      </c>
+      <c r="F168" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>93</v>
       </c>
@@ -4022,8 +4074,14 @@
       <c r="D170" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E170" t="s">
+        <v>93</v>
+      </c>
+      <c r="F170" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>101</v>
       </c>
@@ -4036,8 +4094,14 @@
       <c r="D172" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E172" t="s">
+        <v>84</v>
+      </c>
+      <c r="F172" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>99</v>
       </c>
@@ -4050,8 +4114,14 @@
       <c r="D173" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E173" t="s">
+        <v>99</v>
+      </c>
+      <c r="F173" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>99</v>
       </c>
@@ -4064,8 +4134,14 @@
       <c r="D175" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E175" t="s">
+        <v>168</v>
+      </c>
+      <c r="F175" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>166</v>
       </c>
@@ -4078,13 +4154,130 @@
       <c r="D176" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E176" t="s">
+        <v>168</v>
+      </c>
+      <c r="F176" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>166</v>
       </c>
       <c r="B177" t="s">
         <v>164</v>
+      </c>
+      <c r="E177" t="s">
+        <v>168</v>
+      </c>
+      <c r="F177" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B180" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>99</v>
+      </c>
+      <c r="B181" s="1" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>101</v>
+      </c>
+      <c r="B182" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>99</v>
+      </c>
+      <c r="B183" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B184" s="1"/>
+    </row>
+    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>91</v>
+      </c>
+      <c r="B185" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>91</v>
+      </c>
+      <c r="B186" s="1" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>91</v>
+      </c>
+      <c r="B187" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B188" s="1"/>
+    </row>
+    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>93</v>
+      </c>
+      <c r="B189" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B190" s="1"/>
+    </row>
+    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>101</v>
+      </c>
+      <c r="B191" s="1" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>84</v>
+      </c>
+      <c r="B192" s="1" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B193" s="1"/>
+    </row>
+    <row r="194" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>211</v>
+      </c>
+      <c r="B194" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>99</v>
+      </c>
+      <c r="B195" s="1" t="s">
+        <v>150</v>
       </c>
     </row>
   </sheetData>

--- a/docs/wo.xlsx
+++ b/docs/wo.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\milne\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nmilner\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{137BD0D5-DD3E-4AD2-9DF5-1498CEA1CB33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7FD25D6-8ABB-481C-B2C1-C4B4FE25C442}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{C32645C5-10AA-4D5C-BF11-217FF2F37ECD}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{C32645C5-10AA-4D5C-BF11-217FF2F37ECD}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="837" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="862" uniqueCount="298">
   <si>
     <t>Pause Barbell Lunge</t>
   </si>
@@ -922,6 +922,15 @@
   </si>
   <si>
     <t>RDL to Row</t>
+  </si>
+  <si>
+    <t>Pulse Back Squat</t>
+  </si>
+  <si>
+    <t>Jumping Lunges</t>
+  </si>
+  <si>
+    <t>Quads, Triceps, Glutes</t>
   </si>
 </sst>
 </file>
@@ -1832,7 +1841,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A791CA79-5EDF-4534-95D3-2767A2C8696F}">
-  <dimension ref="A2:S195"/>
+  <dimension ref="A2:S196"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.7109375" customWidth="1"/>
@@ -4179,105 +4188,179 @@
       <c r="B180" t="s">
         <v>292</v>
       </c>
+      <c r="D180" t="s">
+        <v>297</v>
+      </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>99</v>
       </c>
-      <c r="B181" s="1" t="s">
+      <c r="B181" t="s">
         <v>235</v>
+      </c>
+      <c r="C181" t="s">
+        <v>101</v>
+      </c>
+      <c r="D181" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>101</v>
       </c>
-      <c r="B182" s="1" t="s">
+      <c r="B182" t="s">
         <v>64</v>
+      </c>
+      <c r="C182" t="s">
+        <v>101</v>
+      </c>
+      <c r="D182" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>99</v>
       </c>
-      <c r="B183" s="1" t="s">
+      <c r="B183" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B184" s="1"/>
+      <c r="C183" t="s">
+        <v>101</v>
+      </c>
+      <c r="D183" t="s">
+        <v>242</v>
+      </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>91</v>
       </c>
-      <c r="B185" s="1" t="s">
+      <c r="B185" t="s">
         <v>63</v>
+      </c>
+      <c r="C185" t="s">
+        <v>91</v>
+      </c>
+      <c r="D185" s="1" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>91</v>
       </c>
-      <c r="B186" s="1" t="s">
+      <c r="B186" t="s">
         <v>246</v>
+      </c>
+      <c r="C186" t="s">
+        <v>91</v>
+      </c>
+      <c r="D186" s="1" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>91</v>
       </c>
-      <c r="B187" s="1" t="s">
+      <c r="B187" t="s">
         <v>237</v>
       </c>
+      <c r="C187" t="s">
+        <v>107</v>
+      </c>
+      <c r="D187" s="1" t="s">
+        <v>243</v>
+      </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B188" s="1"/>
+      <c r="D188" s="1"/>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>93</v>
       </c>
-      <c r="B189" s="1" t="s">
+      <c r="B189" t="s">
         <v>19</v>
       </c>
+      <c r="C189" t="s">
+        <v>93</v>
+      </c>
+      <c r="D189" s="1" t="s">
+        <v>295</v>
+      </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B190" s="1"/>
+      <c r="D190" s="1"/>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>101</v>
       </c>
-      <c r="B191" s="1" t="s">
+      <c r="B191" t="s">
         <v>294</v>
+      </c>
+      <c r="C191" t="s">
+        <v>101</v>
+      </c>
+      <c r="D191" s="1" t="s">
+        <v>296</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>84</v>
       </c>
-      <c r="B192" s="1" t="s">
+      <c r="B192" t="s">
         <v>293</v>
       </c>
-    </row>
-    <row r="193" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B193" s="1"/>
-    </row>
-    <row r="194" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C192" t="s">
+        <v>99</v>
+      </c>
+      <c r="D192" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D193" s="1"/>
+    </row>
+    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>211</v>
       </c>
-      <c r="B194" s="1" t="s">
+      <c r="B194" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="195" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C194" t="s">
+        <v>99</v>
+      </c>
+      <c r="D194" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>99</v>
       </c>
-      <c r="B195" s="1" t="s">
+      <c r="B195" t="s">
         <v>150</v>
+      </c>
+      <c r="C195" t="s">
+        <v>99</v>
+      </c>
+      <c r="D195" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C196" t="s">
+        <v>99</v>
+      </c>
+      <c r="D196" s="1" t="s">
+        <v>163</v>
       </c>
     </row>
   </sheetData>

--- a/docs/wo.xlsx
+++ b/docs/wo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nmilner\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\milne\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7FD25D6-8ABB-481C-B2C1-C4B4FE25C442}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BB3A1B1-1867-4437-8044-1E62AC9DFC02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{C32645C5-10AA-4D5C-BF11-217FF2F37ECD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{C32645C5-10AA-4D5C-BF11-217FF2F37ECD}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="862" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="912" uniqueCount="298">
   <si>
     <t>Pause Barbell Lunge</t>
   </si>
@@ -966,9 +966,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1841,7 +1840,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A791CA79-5EDF-4534-95D3-2767A2C8696F}">
-  <dimension ref="A2:S196"/>
+  <dimension ref="A2:S214"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.7109375" customWidth="1"/>
@@ -4191,6 +4190,9 @@
       <c r="D180" t="s">
         <v>297</v>
       </c>
+      <c r="F180" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
@@ -4205,6 +4207,12 @@
       <c r="D181" t="s">
         <v>244</v>
       </c>
+      <c r="E181" t="s">
+        <v>101</v>
+      </c>
+      <c r="F181" t="s">
+        <v>270</v>
+      </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
@@ -4219,6 +4227,12 @@
       <c r="D182" t="s">
         <v>68</v>
       </c>
+      <c r="E182" t="s">
+        <v>101</v>
+      </c>
+      <c r="F182" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
@@ -4233,6 +4247,12 @@
       <c r="D183" t="s">
         <v>242</v>
       </c>
+      <c r="E183" t="s">
+        <v>99</v>
+      </c>
+      <c r="F183" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
@@ -4244,8 +4264,14 @@
       <c r="C185" t="s">
         <v>91</v>
       </c>
-      <c r="D185" s="1" t="s">
+      <c r="D185" t="s">
         <v>198</v>
+      </c>
+      <c r="E185" t="s">
+        <v>155</v>
+      </c>
+      <c r="F185" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
@@ -4258,8 +4284,14 @@
       <c r="C186" t="s">
         <v>91</v>
       </c>
-      <c r="D186" s="1" t="s">
+      <c r="D186" t="s">
         <v>206</v>
+      </c>
+      <c r="E186" t="s">
+        <v>91</v>
+      </c>
+      <c r="F186" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
@@ -4272,12 +4304,15 @@
       <c r="C187" t="s">
         <v>107</v>
       </c>
-      <c r="D187" s="1" t="s">
+      <c r="D187" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D188" s="1"/>
+      <c r="E187" t="s">
+        <v>155</v>
+      </c>
+      <c r="F187" t="s">
+        <v>204</v>
+      </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
@@ -4289,12 +4324,15 @@
       <c r="C189" t="s">
         <v>93</v>
       </c>
-      <c r="D189" s="1" t="s">
+      <c r="D189" t="s">
         <v>295</v>
       </c>
-    </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D190" s="1"/>
+      <c r="E189" t="s">
+        <v>93</v>
+      </c>
+      <c r="F189" t="s">
+        <v>213</v>
+      </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
@@ -4306,8 +4344,14 @@
       <c r="C191" t="s">
         <v>101</v>
       </c>
-      <c r="D191" s="1" t="s">
+      <c r="D191" t="s">
         <v>296</v>
+      </c>
+      <c r="E191" t="s">
+        <v>101</v>
+      </c>
+      <c r="F191" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
@@ -4320,14 +4364,17 @@
       <c r="C192" t="s">
         <v>99</v>
       </c>
-      <c r="D192" s="1" t="s">
+      <c r="D192" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D193" s="1"/>
-    </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E192" t="s">
+        <v>101</v>
+      </c>
+      <c r="F192" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>211</v>
       </c>
@@ -4337,11 +4384,17 @@
       <c r="C194" t="s">
         <v>99</v>
       </c>
-      <c r="D194" s="1" t="s">
+      <c r="D194" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E194" t="s">
+        <v>101</v>
+      </c>
+      <c r="F194" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>99</v>
       </c>
@@ -4351,16 +4404,129 @@
       <c r="C195" t="s">
         <v>99</v>
       </c>
-      <c r="D195" s="1" t="s">
+      <c r="D195" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E195" t="s">
+        <v>101</v>
+      </c>
+      <c r="F195" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C196" t="s">
         <v>99</v>
       </c>
-      <c r="D196" s="1" t="s">
+      <c r="D196" t="s">
         <v>163</v>
+      </c>
+      <c r="E196" t="s">
+        <v>127</v>
+      </c>
+      <c r="F196" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B199" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>84</v>
+      </c>
+      <c r="B200" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>101</v>
+      </c>
+      <c r="B201" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>99</v>
+      </c>
+      <c r="B202" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>91</v>
+      </c>
+      <c r="B204" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>155</v>
+      </c>
+      <c r="B205" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>91</v>
+      </c>
+      <c r="B206" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>101</v>
+      </c>
+      <c r="B208" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>101</v>
+      </c>
+      <c r="B209" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>101</v>
+      </c>
+      <c r="B210" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>101</v>
+      </c>
+      <c r="B212" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>101</v>
+      </c>
+      <c r="B213" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>168</v>
+      </c>
+      <c r="B214" t="s">
+        <v>228</v>
       </c>
     </row>
   </sheetData>

--- a/docs/wo.xlsx
+++ b/docs/wo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\milne\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nmilner\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BB3A1B1-1867-4437-8044-1E62AC9DFC02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D6092F8-91CA-47C3-99A3-FD67D2C9C904}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{C32645C5-10AA-4D5C-BF11-217FF2F37ECD}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{C32645C5-10AA-4D5C-BF11-217FF2F37ECD}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="912" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="935" uniqueCount="300">
   <si>
     <t>Pause Barbell Lunge</t>
   </si>
@@ -931,6 +931,12 @@
   </si>
   <si>
     <t>Quads, Triceps, Glutes</t>
+  </si>
+  <si>
+    <t>KB Squats</t>
+  </si>
+  <si>
+    <t>Walking Lunges</t>
   </si>
 </sst>
 </file>
@@ -4432,6 +4438,9 @@
       <c r="B199" t="s">
         <v>252</v>
       </c>
+      <c r="D199" t="s">
+        <v>254</v>
+      </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
@@ -4440,6 +4449,12 @@
       <c r="B200" t="s">
         <v>255</v>
       </c>
+      <c r="C200" t="s">
+        <v>101</v>
+      </c>
+      <c r="D200" t="s">
+        <v>260</v>
+      </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
@@ -4448,6 +4463,12 @@
       <c r="B201" t="s">
         <v>39</v>
       </c>
+      <c r="C201" t="s">
+        <v>101</v>
+      </c>
+      <c r="D201" t="s">
+        <v>222</v>
+      </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
@@ -4456,6 +4477,12 @@
       <c r="B202" t="s">
         <v>171</v>
       </c>
+      <c r="C202" t="s">
+        <v>211</v>
+      </c>
+      <c r="D202" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
@@ -4463,6 +4490,12 @@
       </c>
       <c r="B204" t="s">
         <v>253</v>
+      </c>
+      <c r="C204" t="s">
+        <v>91</v>
+      </c>
+      <c r="D204" t="s">
+        <v>298</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
@@ -4472,6 +4505,12 @@
       <c r="B205" t="s">
         <v>257</v>
       </c>
+      <c r="C205" t="s">
+        <v>91</v>
+      </c>
+      <c r="D205" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
@@ -4480,6 +4519,12 @@
       <c r="B206" t="s">
         <v>258</v>
       </c>
+      <c r="C206" t="s">
+        <v>91</v>
+      </c>
+      <c r="D206" t="s">
+        <v>299</v>
+      </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
@@ -4488,8 +4533,14 @@
       <c r="B208" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="209" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C208" t="s">
+        <v>93</v>
+      </c>
+      <c r="D208" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>101</v>
       </c>
@@ -4497,15 +4548,29 @@
         <v>40</v>
       </c>
     </row>
-    <row r="210" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>101</v>
       </c>
       <c r="B210" t="s">
         <v>259</v>
       </c>
-    </row>
-    <row r="212" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C210" t="s">
+        <v>101</v>
+      </c>
+      <c r="D210" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C211" t="s">
+        <v>99</v>
+      </c>
+      <c r="D211" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>101</v>
       </c>
@@ -4513,20 +4578,32 @@
         <v>179</v>
       </c>
     </row>
-    <row r="213" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>101</v>
       </c>
       <c r="B213" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="214" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C213" t="s">
+        <v>101</v>
+      </c>
+      <c r="D213" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>168</v>
       </c>
       <c r="B214" t="s">
         <v>228</v>
+      </c>
+      <c r="C214" t="s">
+        <v>99</v>
+      </c>
+      <c r="D214" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/docs/wo.xlsx
+++ b/docs/wo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nmilner\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\milne\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D6092F8-91CA-47C3-99A3-FD67D2C9C904}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28543215-3D46-4027-BBAC-95B9F4CBC44F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{C32645C5-10AA-4D5C-BF11-217FF2F37ECD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{C32645C5-10AA-4D5C-BF11-217FF2F37ECD}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="935" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="983" uniqueCount="303">
   <si>
     <t>Pause Barbell Lunge</t>
   </si>
@@ -937,6 +937,15 @@
   </si>
   <si>
     <t>Walking Lunges</t>
+  </si>
+  <si>
+    <t>Sing Arm OH Tricep Ext</t>
+  </si>
+  <si>
+    <t>DB Inc Bench</t>
+  </si>
+  <si>
+    <t>Half Kneeling bottoms up KB Press (down leg)</t>
   </si>
 </sst>
 </file>
@@ -972,8 +981,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1846,7 +1856,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A791CA79-5EDF-4534-95D3-2767A2C8696F}">
-  <dimension ref="A2:S214"/>
+  <dimension ref="A2:S233"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.7109375" customWidth="1"/>
@@ -4337,7 +4347,7 @@
         <v>93</v>
       </c>
       <c r="F189" t="s">
-        <v>213</v>
+        <v>301</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
@@ -4441,6 +4451,9 @@
       <c r="D199" t="s">
         <v>254</v>
       </c>
+      <c r="F199" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
@@ -4455,6 +4468,12 @@
       <c r="D200" t="s">
         <v>260</v>
       </c>
+      <c r="E200" t="s">
+        <v>101</v>
+      </c>
+      <c r="F200" s="1" t="s">
+        <v>264</v>
+      </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
@@ -4469,6 +4488,12 @@
       <c r="D201" t="s">
         <v>222</v>
       </c>
+      <c r="E201" t="s">
+        <v>101</v>
+      </c>
+      <c r="F201" s="1" t="s">
+        <v>300</v>
+      </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
@@ -4483,6 +4508,15 @@
       <c r="D202" t="s">
         <v>190</v>
       </c>
+      <c r="E202" t="s">
+        <v>101</v>
+      </c>
+      <c r="F202" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F203" s="1"/>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
@@ -4496,6 +4530,12 @@
       </c>
       <c r="D204" t="s">
         <v>298</v>
+      </c>
+      <c r="E204" t="s">
+        <v>91</v>
+      </c>
+      <c r="F204" s="1" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
@@ -4511,6 +4551,12 @@
       <c r="D205" t="s">
         <v>19</v>
       </c>
+      <c r="E205" t="s">
+        <v>91</v>
+      </c>
+      <c r="F205" s="1" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
@@ -4525,6 +4571,15 @@
       <c r="D206" t="s">
         <v>299</v>
       </c>
+      <c r="E206" t="s">
+        <v>91</v>
+      </c>
+      <c r="F206" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F207" s="1"/>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
@@ -4539,16 +4594,23 @@
       <c r="D208" t="s">
         <v>273</v>
       </c>
-    </row>
-    <row r="209" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E208" t="s">
+        <v>93</v>
+      </c>
+      <c r="F208" s="1" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>101</v>
       </c>
       <c r="B209" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="210" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F209" s="1"/>
+    </row>
+    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>101</v>
       </c>
@@ -4561,24 +4623,37 @@
       <c r="D210" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="211" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E210" t="s">
+        <v>99</v>
+      </c>
+      <c r="F210" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C211" t="s">
         <v>99</v>
       </c>
       <c r="D211" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="212" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E211" t="s">
+        <v>84</v>
+      </c>
+      <c r="F211" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>101</v>
       </c>
       <c r="B212" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="213" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F212" s="1"/>
+    </row>
+    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>101</v>
       </c>
@@ -4591,8 +4666,14 @@
       <c r="D213" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="214" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E213" t="s">
+        <v>99</v>
+      </c>
+      <c r="F213" s="1" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>168</v>
       </c>
@@ -4604,6 +4685,113 @@
       </c>
       <c r="D214" t="s">
         <v>44</v>
+      </c>
+      <c r="E214" t="s">
+        <v>99</v>
+      </c>
+      <c r="F214" s="1" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B217" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>101</v>
+      </c>
+      <c r="B218" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>101</v>
+      </c>
+      <c r="B219" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>101</v>
+      </c>
+      <c r="B220" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>91</v>
+      </c>
+      <c r="B222" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="223" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>91</v>
+      </c>
+      <c r="B223" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>91</v>
+      </c>
+      <c r="B224" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
+        <v>93</v>
+      </c>
+      <c r="B226" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A228" t="s">
+        <v>101</v>
+      </c>
+      <c r="B228" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
+        <v>101</v>
+      </c>
+      <c r="B229" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A231" t="s">
+        <v>168</v>
+      </c>
+      <c r="B231" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A232" t="s">
+        <v>166</v>
+      </c>
+      <c r="B232" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>99</v>
+      </c>
+      <c r="B233" t="s">
+        <v>163</v>
       </c>
     </row>
   </sheetData>

--- a/docs/wo.xlsx
+++ b/docs/wo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\milne\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28543215-3D46-4027-BBAC-95B9F4CBC44F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A72C04A-F35D-4F60-BAD8-74BD703971EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{C32645C5-10AA-4D5C-BF11-217FF2F37ECD}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="983" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1177" uniqueCount="305">
   <si>
     <t>Pause Barbell Lunge</t>
   </si>
@@ -946,6 +946,12 @@
   </si>
   <si>
     <t>Half Kneeling bottoms up KB Press (down leg)</t>
+  </si>
+  <si>
+    <t>Inc Bench Curls</t>
+  </si>
+  <si>
+    <t>BB Rev Grip Curl</t>
   </si>
 </sst>
 </file>
@@ -981,9 +987,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1856,7 +1861,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A791CA79-5EDF-4534-95D3-2767A2C8696F}">
-  <dimension ref="A2:S233"/>
+  <dimension ref="A2:S271"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.7109375" customWidth="1"/>
@@ -4471,7 +4476,7 @@
       <c r="E200" t="s">
         <v>101</v>
       </c>
-      <c r="F200" s="1" t="s">
+      <c r="F200" t="s">
         <v>264</v>
       </c>
     </row>
@@ -4491,7 +4496,7 @@
       <c r="E201" t="s">
         <v>101</v>
       </c>
-      <c r="F201" s="1" t="s">
+      <c r="F201" t="s">
         <v>300</v>
       </c>
     </row>
@@ -4511,12 +4516,9 @@
       <c r="E202" t="s">
         <v>101</v>
       </c>
-      <c r="F202" s="1" t="s">
+      <c r="F202" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F203" s="1"/>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
@@ -4534,7 +4536,7 @@
       <c r="E204" t="s">
         <v>91</v>
       </c>
-      <c r="F204" s="1" t="s">
+      <c r="F204" t="s">
         <v>157</v>
       </c>
     </row>
@@ -4554,7 +4556,7 @@
       <c r="E205" t="s">
         <v>91</v>
       </c>
-      <c r="F205" s="1" t="s">
+      <c r="F205" t="s">
         <v>49</v>
       </c>
     </row>
@@ -4574,12 +4576,9 @@
       <c r="E206" t="s">
         <v>91</v>
       </c>
-      <c r="F206" s="1" t="s">
+      <c r="F206" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F207" s="1"/>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
@@ -4597,7 +4596,7 @@
       <c r="E208" t="s">
         <v>93</v>
       </c>
-      <c r="F208" s="1" t="s">
+      <c r="F208" t="s">
         <v>266</v>
       </c>
     </row>
@@ -4608,7 +4607,6 @@
       <c r="B209" t="s">
         <v>40</v>
       </c>
-      <c r="F209" s="1"/>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
@@ -4626,7 +4624,7 @@
       <c r="E210" t="s">
         <v>99</v>
       </c>
-      <c r="F210" s="1" t="s">
+      <c r="F210" t="s">
         <v>81</v>
       </c>
     </row>
@@ -4640,7 +4638,7 @@
       <c r="E211" t="s">
         <v>84</v>
       </c>
-      <c r="F211" s="1" t="s">
+      <c r="F211" t="s">
         <v>46</v>
       </c>
     </row>
@@ -4651,7 +4649,6 @@
       <c r="B212" t="s">
         <v>179</v>
       </c>
-      <c r="F212" s="1"/>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
@@ -4669,7 +4666,7 @@
       <c r="E213" t="s">
         <v>99</v>
       </c>
-      <c r="F213" s="1" t="s">
+      <c r="F213" t="s">
         <v>267</v>
       </c>
     </row>
@@ -4689,7 +4686,7 @@
       <c r="E214" t="s">
         <v>99</v>
       </c>
-      <c r="F214" s="1" t="s">
+      <c r="F214" t="s">
         <v>268</v>
       </c>
     </row>
@@ -4697,6 +4694,12 @@
       <c r="B217" t="s">
         <v>269</v>
       </c>
+      <c r="D217" t="s">
+        <v>272</v>
+      </c>
+      <c r="F217" t="s">
+        <v>278</v>
+      </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
@@ -4705,6 +4708,18 @@
       <c r="B218" t="s">
         <v>235</v>
       </c>
+      <c r="C218" t="s">
+        <v>101</v>
+      </c>
+      <c r="D218" t="s">
+        <v>227</v>
+      </c>
+      <c r="E218" t="s">
+        <v>99</v>
+      </c>
+      <c r="F218" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
@@ -4713,6 +4728,18 @@
       <c r="B219" t="s">
         <v>302</v>
       </c>
+      <c r="C219" t="s">
+        <v>101</v>
+      </c>
+      <c r="D219" t="s">
+        <v>274</v>
+      </c>
+      <c r="E219" t="s">
+        <v>99</v>
+      </c>
+      <c r="F219" t="s">
+        <v>191</v>
+      </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
@@ -4721,6 +4748,18 @@
       <c r="B220" t="s">
         <v>33</v>
       </c>
+      <c r="C220" t="s">
+        <v>99</v>
+      </c>
+      <c r="D220" t="s">
+        <v>239</v>
+      </c>
+      <c r="E220" t="s">
+        <v>99</v>
+      </c>
+      <c r="F220" t="s">
+        <v>282</v>
+      </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
@@ -4729,6 +4768,18 @@
       <c r="B222" t="s">
         <v>9</v>
       </c>
+      <c r="C222" t="s">
+        <v>91</v>
+      </c>
+      <c r="D222" t="s">
+        <v>273</v>
+      </c>
+      <c r="E222" t="s">
+        <v>91</v>
+      </c>
+      <c r="F222" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
@@ -4737,6 +4788,18 @@
       <c r="B223" t="s">
         <v>30</v>
       </c>
+      <c r="C223" t="s">
+        <v>155</v>
+      </c>
+      <c r="D223" t="s">
+        <v>55</v>
+      </c>
+      <c r="E223" t="s">
+        <v>91</v>
+      </c>
+      <c r="F223" t="s">
+        <v>237</v>
+      </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
@@ -4745,53 +4808,625 @@
       <c r="B224" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="226" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C224" t="s">
+        <v>114</v>
+      </c>
+      <c r="D224" t="s">
+        <v>115</v>
+      </c>
+      <c r="E224" t="s">
+        <v>155</v>
+      </c>
+      <c r="F224" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>93</v>
       </c>
       <c r="B226" t="s">
         <v>246</v>
       </c>
-    </row>
-    <row r="228" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C226" t="s">
+        <v>277</v>
+      </c>
+      <c r="D226" t="s">
+        <v>276</v>
+      </c>
+      <c r="E226" t="s">
+        <v>93</v>
+      </c>
+      <c r="F226" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C227" t="s">
+        <v>101</v>
+      </c>
+      <c r="D227" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>101</v>
       </c>
       <c r="B228" t="s">
         <v>289</v>
       </c>
-    </row>
-    <row r="229" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C228" t="s">
+        <v>99</v>
+      </c>
+      <c r="D228" t="s">
+        <v>159</v>
+      </c>
+      <c r="E228" t="s">
+        <v>99</v>
+      </c>
+      <c r="F228" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>101</v>
       </c>
       <c r="B229" t="s">
         <v>271</v>
       </c>
-    </row>
-    <row r="231" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E229" t="s">
+        <v>84</v>
+      </c>
+      <c r="F229" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C230" t="s">
+        <v>211</v>
+      </c>
+      <c r="D230" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>168</v>
       </c>
       <c r="B231" t="s">
         <v>228</v>
       </c>
-    </row>
-    <row r="232" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C231" t="s">
+        <v>99</v>
+      </c>
+      <c r="D231" t="s">
+        <v>150</v>
+      </c>
+      <c r="E231" t="s">
+        <v>84</v>
+      </c>
+      <c r="F231" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>166</v>
       </c>
       <c r="B232" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="233" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E232" t="s">
+        <v>99</v>
+      </c>
+      <c r="F232" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>99</v>
       </c>
       <c r="B233" t="s">
         <v>163</v>
+      </c>
+      <c r="E233" t="s">
+        <v>101</v>
+      </c>
+      <c r="F233" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B236" t="s">
+        <v>283</v>
+      </c>
+      <c r="D236" t="s">
+        <v>287</v>
+      </c>
+      <c r="F236" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="237" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A237" t="s">
+        <v>101</v>
+      </c>
+      <c r="B237" t="s">
+        <v>182</v>
+      </c>
+      <c r="C237" t="s">
+        <v>101</v>
+      </c>
+      <c r="D237" t="s">
+        <v>121</v>
+      </c>
+      <c r="E237" t="s">
+        <v>101</v>
+      </c>
+      <c r="F237" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="238" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A238" t="s">
+        <v>101</v>
+      </c>
+      <c r="B238" t="s">
+        <v>286</v>
+      </c>
+      <c r="C238" t="s">
+        <v>101</v>
+      </c>
+      <c r="D238" t="s">
+        <v>290</v>
+      </c>
+      <c r="E238" t="s">
+        <v>101</v>
+      </c>
+      <c r="F238" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="239" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A239" t="s">
+        <v>84</v>
+      </c>
+      <c r="B239" t="s">
+        <v>285</v>
+      </c>
+      <c r="C239" t="s">
+        <v>101</v>
+      </c>
+      <c r="D239" t="s">
+        <v>288</v>
+      </c>
+      <c r="E239" t="s">
+        <v>99</v>
+      </c>
+      <c r="F239" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A241" t="s">
+        <v>91</v>
+      </c>
+      <c r="B241" t="s">
+        <v>284</v>
+      </c>
+      <c r="C241" t="s">
+        <v>91</v>
+      </c>
+      <c r="D241" t="s">
+        <v>70</v>
+      </c>
+      <c r="E241" t="s">
+        <v>91</v>
+      </c>
+      <c r="F241" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="242" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A242" t="s">
+        <v>91</v>
+      </c>
+      <c r="B242" t="s">
+        <v>258</v>
+      </c>
+      <c r="C242" t="s">
+        <v>91</v>
+      </c>
+      <c r="D242" t="s">
+        <v>260</v>
+      </c>
+      <c r="E242" t="s">
+        <v>91</v>
+      </c>
+      <c r="F242" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="243" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A243" t="s">
+        <v>91</v>
+      </c>
+      <c r="B243" t="s">
+        <v>27</v>
+      </c>
+      <c r="C243" t="s">
+        <v>91</v>
+      </c>
+      <c r="D243" t="s">
+        <v>202</v>
+      </c>
+      <c r="E243" t="s">
+        <v>155</v>
+      </c>
+      <c r="F243" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="245" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A245" t="s">
+        <v>93</v>
+      </c>
+      <c r="B245" t="s">
+        <v>30</v>
+      </c>
+      <c r="C245" t="s">
+        <v>93</v>
+      </c>
+      <c r="D245" t="s">
+        <v>245</v>
+      </c>
+      <c r="E245" t="s">
+        <v>93</v>
+      </c>
+      <c r="F245" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="247" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A247" t="s">
+        <v>101</v>
+      </c>
+      <c r="B247" t="s">
+        <v>39</v>
+      </c>
+      <c r="C247" t="s">
+        <v>101</v>
+      </c>
+      <c r="D247" t="s">
+        <v>53</v>
+      </c>
+      <c r="E247" t="s">
+        <v>84</v>
+      </c>
+      <c r="F247" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="248" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A248" t="s">
+        <v>99</v>
+      </c>
+      <c r="B248" t="s">
+        <v>157</v>
+      </c>
+      <c r="C248" t="s">
+        <v>101</v>
+      </c>
+      <c r="D248" t="s">
+        <v>172</v>
+      </c>
+      <c r="E248" t="s">
+        <v>99</v>
+      </c>
+      <c r="F248" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="250" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A250" t="s">
+        <v>99</v>
+      </c>
+      <c r="B250" t="s">
+        <v>163</v>
+      </c>
+      <c r="C250" t="s">
+        <v>101</v>
+      </c>
+      <c r="D250" t="s">
+        <v>45</v>
+      </c>
+      <c r="E250" t="s">
+        <v>168</v>
+      </c>
+      <c r="F250" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="251" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A251" t="s">
+        <v>166</v>
+      </c>
+      <c r="B251" t="s">
+        <v>165</v>
+      </c>
+      <c r="C251" t="s">
+        <v>99</v>
+      </c>
+      <c r="D251" t="s">
+        <v>44</v>
+      </c>
+      <c r="E251" t="s">
+        <v>168</v>
+      </c>
+      <c r="F251" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="252" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A252" t="s">
+        <v>166</v>
+      </c>
+      <c r="B252" t="s">
+        <v>164</v>
+      </c>
+      <c r="E252" t="s">
+        <v>168</v>
+      </c>
+      <c r="F252" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="255" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B255" t="s">
+        <v>292</v>
+      </c>
+      <c r="D255" t="s">
+        <v>297</v>
+      </c>
+      <c r="F255" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="256" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A256" t="s">
+        <v>99</v>
+      </c>
+      <c r="B256" t="s">
+        <v>235</v>
+      </c>
+      <c r="C256" t="s">
+        <v>101</v>
+      </c>
+      <c r="D256" t="s">
+        <v>244</v>
+      </c>
+      <c r="E256" t="s">
+        <v>101</v>
+      </c>
+      <c r="F256" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A257" t="s">
+        <v>101</v>
+      </c>
+      <c r="B257" t="s">
+        <v>64</v>
+      </c>
+      <c r="C257" t="s">
+        <v>101</v>
+      </c>
+      <c r="D257" t="s">
+        <v>68</v>
+      </c>
+      <c r="E257" t="s">
+        <v>101</v>
+      </c>
+      <c r="F257" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="258" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A258" t="s">
+        <v>99</v>
+      </c>
+      <c r="B258" t="s">
+        <v>154</v>
+      </c>
+      <c r="C258" t="s">
+        <v>101</v>
+      </c>
+      <c r="D258" t="s">
+        <v>242</v>
+      </c>
+      <c r="E258" t="s">
+        <v>99</v>
+      </c>
+      <c r="F258" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A260" t="s">
+        <v>91</v>
+      </c>
+      <c r="B260" t="s">
+        <v>63</v>
+      </c>
+      <c r="C260" t="s">
+        <v>91</v>
+      </c>
+      <c r="D260" t="s">
+        <v>198</v>
+      </c>
+      <c r="E260" t="s">
+        <v>155</v>
+      </c>
+      <c r="F260" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A261" t="s">
+        <v>91</v>
+      </c>
+      <c r="B261" t="s">
+        <v>246</v>
+      </c>
+      <c r="C261" t="s">
+        <v>91</v>
+      </c>
+      <c r="D261" t="s">
+        <v>206</v>
+      </c>
+      <c r="E261" t="s">
+        <v>91</v>
+      </c>
+      <c r="F261" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A262" t="s">
+        <v>91</v>
+      </c>
+      <c r="B262" t="s">
+        <v>237</v>
+      </c>
+      <c r="C262" t="s">
+        <v>91</v>
+      </c>
+      <c r="D262" t="s">
+        <v>273</v>
+      </c>
+      <c r="E262" t="s">
+        <v>155</v>
+      </c>
+      <c r="F262" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="264" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A264" t="s">
+        <v>93</v>
+      </c>
+      <c r="B264" t="s">
+        <v>19</v>
+      </c>
+      <c r="C264" t="s">
+        <v>93</v>
+      </c>
+      <c r="D264" t="s">
+        <v>295</v>
+      </c>
+      <c r="E264" t="s">
+        <v>93</v>
+      </c>
+      <c r="F264" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A266" t="s">
+        <v>101</v>
+      </c>
+      <c r="B266" t="s">
+        <v>294</v>
+      </c>
+      <c r="C266" t="s">
+        <v>101</v>
+      </c>
+      <c r="D266" t="s">
+        <v>296</v>
+      </c>
+      <c r="E266" t="s">
+        <v>101</v>
+      </c>
+      <c r="F266" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="267" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A267" t="s">
+        <v>84</v>
+      </c>
+      <c r="B267" t="s">
+        <v>293</v>
+      </c>
+      <c r="C267" t="s">
+        <v>99</v>
+      </c>
+      <c r="D267" t="s">
+        <v>81</v>
+      </c>
+      <c r="E267" t="s">
+        <v>101</v>
+      </c>
+      <c r="F267" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A269" t="s">
+        <v>211</v>
+      </c>
+      <c r="B269" t="s">
+        <v>61</v>
+      </c>
+      <c r="C269" t="s">
+        <v>99</v>
+      </c>
+      <c r="D269" t="s">
+        <v>66</v>
+      </c>
+      <c r="E269" t="s">
+        <v>101</v>
+      </c>
+      <c r="F269" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="270" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A270" t="s">
+        <v>99</v>
+      </c>
+      <c r="B270" t="s">
+        <v>150</v>
+      </c>
+      <c r="C270" t="s">
+        <v>99</v>
+      </c>
+      <c r="D270" t="s">
+        <v>54</v>
+      </c>
+      <c r="E270" t="s">
+        <v>101</v>
+      </c>
+      <c r="F270" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="271" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C271" t="s">
+        <v>99</v>
+      </c>
+      <c r="D271" t="s">
+        <v>163</v>
+      </c>
+      <c r="E271" t="s">
+        <v>127</v>
+      </c>
+      <c r="F271" t="s">
+        <v>126</v>
       </c>
     </row>
   </sheetData>

--- a/docs/wo.xlsx
+++ b/docs/wo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\milne\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A72C04A-F35D-4F60-BAD8-74BD703971EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{644A64B7-48DE-4E37-8138-9096090A29C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{C32645C5-10AA-4D5C-BF11-217FF2F37ECD}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1177" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1321" uniqueCount="314">
   <si>
     <t>Pause Barbell Lunge</t>
   </si>
@@ -952,6 +952,33 @@
   </si>
   <si>
     <t>BB Rev Grip Curl</t>
+  </si>
+  <si>
+    <t>Wide Curl</t>
+  </si>
+  <si>
+    <t>Deficit Rows</t>
+  </si>
+  <si>
+    <t>DB BOR</t>
+  </si>
+  <si>
+    <t>Rev. Grip Pushdowns</t>
+  </si>
+  <si>
+    <t>Deficit Push Ups</t>
+  </si>
+  <si>
+    <t>Floor Press</t>
+  </si>
+  <si>
+    <t>Skullcrushers</t>
+  </si>
+  <si>
+    <t>Elevated Hip Thrust</t>
+  </si>
+  <si>
+    <t>DB RDL to Shrug</t>
   </si>
 </sst>
 </file>
@@ -1861,7 +1888,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A791CA79-5EDF-4534-95D3-2767A2C8696F}">
-  <dimension ref="A2:S271"/>
+  <dimension ref="A2:S307"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.7109375" customWidth="1"/>
@@ -5429,6 +5456,496 @@
         <v>126</v>
       </c>
     </row>
+    <row r="273" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B273" t="s">
+        <v>252</v>
+      </c>
+      <c r="D273" t="s">
+        <v>254</v>
+      </c>
+      <c r="F273" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="274" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A274" t="s">
+        <v>101</v>
+      </c>
+      <c r="B274" t="s">
+        <v>255</v>
+      </c>
+      <c r="C274" t="s">
+        <v>101</v>
+      </c>
+      <c r="D274" t="s">
+        <v>260</v>
+      </c>
+      <c r="E274" t="s">
+        <v>101</v>
+      </c>
+      <c r="F274" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="275" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A275" t="s">
+        <v>101</v>
+      </c>
+      <c r="B275" t="s">
+        <v>39</v>
+      </c>
+      <c r="C275" t="s">
+        <v>101</v>
+      </c>
+      <c r="D275" t="s">
+        <v>306</v>
+      </c>
+      <c r="E275" t="s">
+        <v>101</v>
+      </c>
+      <c r="F275" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="276" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A276" t="s">
+        <v>99</v>
+      </c>
+      <c r="B276" t="s">
+        <v>55</v>
+      </c>
+      <c r="C276" t="s">
+        <v>211</v>
+      </c>
+      <c r="D276" t="s">
+        <v>190</v>
+      </c>
+      <c r="E276" t="s">
+        <v>101</v>
+      </c>
+      <c r="F276" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="278" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A278" t="s">
+        <v>91</v>
+      </c>
+      <c r="B278" t="s">
+        <v>253</v>
+      </c>
+      <c r="C278" t="s">
+        <v>91</v>
+      </c>
+      <c r="D278" t="s">
+        <v>263</v>
+      </c>
+      <c r="E278" t="s">
+        <v>91</v>
+      </c>
+      <c r="F278" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="279" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A279" t="s">
+        <v>91</v>
+      </c>
+      <c r="B279" t="s">
+        <v>40</v>
+      </c>
+      <c r="C279" t="s">
+        <v>91</v>
+      </c>
+      <c r="D279" t="s">
+        <v>19</v>
+      </c>
+      <c r="E279" t="s">
+        <v>91</v>
+      </c>
+      <c r="F279" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="280" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A280" t="s">
+        <v>91</v>
+      </c>
+      <c r="B280" t="s">
+        <v>258</v>
+      </c>
+      <c r="C280" t="s">
+        <v>91</v>
+      </c>
+      <c r="D280" t="s">
+        <v>262</v>
+      </c>
+      <c r="E280" t="s">
+        <v>91</v>
+      </c>
+      <c r="F280" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="282" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A282" t="s">
+        <v>101</v>
+      </c>
+      <c r="B282" t="s">
+        <v>256</v>
+      </c>
+      <c r="C282" t="s">
+        <v>93</v>
+      </c>
+      <c r="D282" t="s">
+        <v>273</v>
+      </c>
+      <c r="E282" t="s">
+        <v>93</v>
+      </c>
+      <c r="F282" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="283" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A283" t="s">
+        <v>101</v>
+      </c>
+      <c r="B283" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="284" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A284" t="s">
+        <v>101</v>
+      </c>
+      <c r="B284" t="s">
+        <v>33</v>
+      </c>
+      <c r="C284" t="s">
+        <v>101</v>
+      </c>
+      <c r="D284" t="s">
+        <v>307</v>
+      </c>
+      <c r="E284" t="s">
+        <v>99</v>
+      </c>
+      <c r="F284" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="285" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C285" t="s">
+        <v>99</v>
+      </c>
+      <c r="D285" t="s">
+        <v>261</v>
+      </c>
+      <c r="E285" t="s">
+        <v>101</v>
+      </c>
+      <c r="F285" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="286" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A286" t="s">
+        <v>101</v>
+      </c>
+      <c r="B286" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="287" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A287" t="s">
+        <v>101</v>
+      </c>
+      <c r="B287" t="s">
+        <v>124</v>
+      </c>
+      <c r="C287" t="s">
+        <v>101</v>
+      </c>
+      <c r="D287" t="s">
+        <v>45</v>
+      </c>
+      <c r="E287" t="s">
+        <v>99</v>
+      </c>
+      <c r="F287" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="288" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A288" t="s">
+        <v>168</v>
+      </c>
+      <c r="B288" t="s">
+        <v>228</v>
+      </c>
+      <c r="C288" t="s">
+        <v>99</v>
+      </c>
+      <c r="D288" t="s">
+        <v>44</v>
+      </c>
+      <c r="E288" t="s">
+        <v>99</v>
+      </c>
+      <c r="F288" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="291" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B291" t="s">
+        <v>269</v>
+      </c>
+      <c r="D291" t="s">
+        <v>272</v>
+      </c>
+      <c r="F291" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="292" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A292" t="s">
+        <v>101</v>
+      </c>
+      <c r="B292" t="s">
+        <v>235</v>
+      </c>
+      <c r="C292" t="s">
+        <v>101</v>
+      </c>
+      <c r="D292" t="s">
+        <v>227</v>
+      </c>
+      <c r="E292" t="s">
+        <v>99</v>
+      </c>
+      <c r="F292" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="293" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A293" t="s">
+        <v>101</v>
+      </c>
+      <c r="B293" t="s">
+        <v>121</v>
+      </c>
+      <c r="C293" t="s">
+        <v>101</v>
+      </c>
+      <c r="D293" t="s">
+        <v>274</v>
+      </c>
+      <c r="E293" t="s">
+        <v>99</v>
+      </c>
+      <c r="F293" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="294" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A294" t="s">
+        <v>99</v>
+      </c>
+      <c r="B294" t="s">
+        <v>312</v>
+      </c>
+      <c r="C294" t="s">
+        <v>99</v>
+      </c>
+      <c r="D294" t="s">
+        <v>239</v>
+      </c>
+      <c r="E294" t="s">
+        <v>99</v>
+      </c>
+      <c r="F294" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="296" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A296" t="s">
+        <v>91</v>
+      </c>
+      <c r="B296" t="s">
+        <v>9</v>
+      </c>
+      <c r="C296" t="s">
+        <v>91</v>
+      </c>
+      <c r="D296" t="s">
+        <v>273</v>
+      </c>
+      <c r="E296" t="s">
+        <v>91</v>
+      </c>
+      <c r="F296" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="297" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A297" t="s">
+        <v>91</v>
+      </c>
+      <c r="B297" t="s">
+        <v>30</v>
+      </c>
+      <c r="C297" t="s">
+        <v>155</v>
+      </c>
+      <c r="D297" t="s">
+        <v>55</v>
+      </c>
+      <c r="E297" t="s">
+        <v>91</v>
+      </c>
+      <c r="F297" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="298" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A298" t="s">
+        <v>91</v>
+      </c>
+      <c r="B298" t="s">
+        <v>202</v>
+      </c>
+      <c r="C298" t="s">
+        <v>114</v>
+      </c>
+      <c r="D298" t="s">
+        <v>115</v>
+      </c>
+      <c r="E298" t="s">
+        <v>155</v>
+      </c>
+      <c r="F298" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="300" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A300" t="s">
+        <v>93</v>
+      </c>
+      <c r="B300" t="s">
+        <v>246</v>
+      </c>
+      <c r="C300" t="s">
+        <v>277</v>
+      </c>
+      <c r="D300" t="s">
+        <v>276</v>
+      </c>
+      <c r="E300" t="s">
+        <v>93</v>
+      </c>
+      <c r="F300" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="301" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C301" t="s">
+        <v>101</v>
+      </c>
+      <c r="D301" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="302" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A302" t="s">
+        <v>101</v>
+      </c>
+      <c r="B302" t="s">
+        <v>288</v>
+      </c>
+      <c r="C302" t="s">
+        <v>99</v>
+      </c>
+      <c r="D302" t="s">
+        <v>159</v>
+      </c>
+      <c r="E302" t="s">
+        <v>99</v>
+      </c>
+      <c r="F302" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="303" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A303" t="s">
+        <v>101</v>
+      </c>
+      <c r="B303" t="s">
+        <v>313</v>
+      </c>
+      <c r="E303" t="s">
+        <v>84</v>
+      </c>
+      <c r="F303" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="304" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C304" t="s">
+        <v>211</v>
+      </c>
+      <c r="D304" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="305" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A305" t="s">
+        <v>168</v>
+      </c>
+      <c r="B305" t="s">
+        <v>228</v>
+      </c>
+      <c r="C305" t="s">
+        <v>99</v>
+      </c>
+      <c r="D305" t="s">
+        <v>150</v>
+      </c>
+      <c r="E305" t="s">
+        <v>84</v>
+      </c>
+      <c r="F305" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="306" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A306" t="s">
+        <v>166</v>
+      </c>
+      <c r="B306" t="s">
+        <v>180</v>
+      </c>
+      <c r="E306" t="s">
+        <v>99</v>
+      </c>
+      <c r="F306" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="307" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A307" t="s">
+        <v>99</v>
+      </c>
+      <c r="B307" t="s">
+        <v>163</v>
+      </c>
+      <c r="E307" t="s">
+        <v>101</v>
+      </c>
+      <c r="F307" t="s">
+        <v>60</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docs/wo.xlsx
+++ b/docs/wo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\milne\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nmilner\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{644A64B7-48DE-4E37-8138-9096090A29C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44D2061A-8396-421F-8C4F-2739166C64F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{C32645C5-10AA-4D5C-BF11-217FF2F37ECD}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{C32645C5-10AA-4D5C-BF11-217FF2F37ECD}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1321" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1369" uniqueCount="314">
   <si>
     <t>Pause Barbell Lunge</t>
   </si>
@@ -1888,7 +1888,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A791CA79-5EDF-4534-95D3-2767A2C8696F}">
-  <dimension ref="A2:S307"/>
+  <dimension ref="A2:S326"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.7109375" customWidth="1"/>
@@ -5946,6 +5946,176 @@
         <v>60</v>
       </c>
     </row>
+    <row r="310" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B310" t="s">
+        <v>283</v>
+      </c>
+      <c r="D310" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="311" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A311" t="s">
+        <v>101</v>
+      </c>
+      <c r="B311" t="s">
+        <v>182</v>
+      </c>
+      <c r="C311" t="s">
+        <v>101</v>
+      </c>
+      <c r="D311" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="312" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A312" t="s">
+        <v>101</v>
+      </c>
+      <c r="B312" t="s">
+        <v>286</v>
+      </c>
+      <c r="C312" t="s">
+        <v>101</v>
+      </c>
+      <c r="D312" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="313" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A313" t="s">
+        <v>84</v>
+      </c>
+      <c r="B313" t="s">
+        <v>285</v>
+      </c>
+      <c r="C313" t="s">
+        <v>101</v>
+      </c>
+      <c r="D313" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="315" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A315" t="s">
+        <v>91</v>
+      </c>
+      <c r="B315" t="s">
+        <v>284</v>
+      </c>
+      <c r="C315" t="s">
+        <v>91</v>
+      </c>
+      <c r="D315" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="316" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A316" t="s">
+        <v>91</v>
+      </c>
+      <c r="B316" t="s">
+        <v>258</v>
+      </c>
+      <c r="C316" t="s">
+        <v>91</v>
+      </c>
+      <c r="D316" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="317" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A317" t="s">
+        <v>91</v>
+      </c>
+      <c r="B317" t="s">
+        <v>27</v>
+      </c>
+      <c r="C317" t="s">
+        <v>91</v>
+      </c>
+      <c r="D317" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="319" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A319" t="s">
+        <v>93</v>
+      </c>
+      <c r="B319" t="s">
+        <v>30</v>
+      </c>
+      <c r="C319" t="s">
+        <v>93</v>
+      </c>
+      <c r="D319" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="321" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A321" t="s">
+        <v>101</v>
+      </c>
+      <c r="B321" t="s">
+        <v>39</v>
+      </c>
+      <c r="C321" t="s">
+        <v>101</v>
+      </c>
+      <c r="D321" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="322" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A322" t="s">
+        <v>99</v>
+      </c>
+      <c r="B322" t="s">
+        <v>157</v>
+      </c>
+      <c r="C322" t="s">
+        <v>101</v>
+      </c>
+      <c r="D322" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="324" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A324" t="s">
+        <v>99</v>
+      </c>
+      <c r="B324" t="s">
+        <v>163</v>
+      </c>
+      <c r="C324" t="s">
+        <v>101</v>
+      </c>
+      <c r="D324" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="325" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A325" t="s">
+        <v>166</v>
+      </c>
+      <c r="B325" t="s">
+        <v>165</v>
+      </c>
+      <c r="C325" t="s">
+        <v>99</v>
+      </c>
+      <c r="D325" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="326" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A326" t="s">
+        <v>166</v>
+      </c>
+      <c r="B326" t="s">
+        <v>164</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docs/wo.xlsx
+++ b/docs/wo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nmilner\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\milne\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44D2061A-8396-421F-8C4F-2739166C64F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBC733CE-D42D-4BC6-BF5B-1781D3A90779}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{C32645C5-10AA-4D5C-BF11-217FF2F37ECD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{C32645C5-10AA-4D5C-BF11-217FF2F37ECD}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1369" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1515" uniqueCount="314">
   <si>
     <t>Pause Barbell Lunge</t>
   </si>
@@ -1888,7 +1888,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A791CA79-5EDF-4534-95D3-2767A2C8696F}">
-  <dimension ref="A2:S326"/>
+  <dimension ref="A2:S362"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.7109375" customWidth="1"/>
@@ -5953,6 +5953,9 @@
       <c r="D310" t="s">
         <v>287</v>
       </c>
+      <c r="F310" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
@@ -5962,11 +5965,17 @@
         <v>182</v>
       </c>
       <c r="C311" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D311" t="s">
         <v>121</v>
       </c>
+      <c r="E311" t="s">
+        <v>101</v>
+      </c>
+      <c r="F311" t="s">
+        <v>303</v>
+      </c>
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
@@ -5980,6 +5989,12 @@
       </c>
       <c r="D312" t="s">
         <v>290</v>
+      </c>
+      <c r="E312" t="s">
+        <v>101</v>
+      </c>
+      <c r="F312" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.25">
@@ -5995,6 +6010,12 @@
       <c r="D313" t="s">
         <v>288</v>
       </c>
+      <c r="E313" t="s">
+        <v>99</v>
+      </c>
+      <c r="F313" t="s">
+        <v>304</v>
+      </c>
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
@@ -6009,6 +6030,12 @@
       <c r="D315" t="s">
         <v>70</v>
       </c>
+      <c r="E315" t="s">
+        <v>91</v>
+      </c>
+      <c r="F315" t="s">
+        <v>223</v>
+      </c>
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
@@ -6023,6 +6050,12 @@
       <c r="D316" t="s">
         <v>260</v>
       </c>
+      <c r="E316" t="s">
+        <v>91</v>
+      </c>
+      <c r="F316" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
@@ -6036,6 +6069,12 @@
       </c>
       <c r="D317" t="s">
         <v>202</v>
+      </c>
+      <c r="E317" t="s">
+        <v>155</v>
+      </c>
+      <c r="F317" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.25">
@@ -6051,8 +6090,14 @@
       <c r="D319" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="321" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E319" t="s">
+        <v>93</v>
+      </c>
+      <c r="F319" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="321" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>101</v>
       </c>
@@ -6065,8 +6110,14 @@
       <c r="D321" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="322" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E321" t="s">
+        <v>84</v>
+      </c>
+      <c r="F321" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="322" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>99</v>
       </c>
@@ -6079,8 +6130,14 @@
       <c r="D322" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="324" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E322" t="s">
+        <v>99</v>
+      </c>
+      <c r="F322" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="324" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>99</v>
       </c>
@@ -6093,8 +6150,14 @@
       <c r="D324" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="325" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E324" t="s">
+        <v>168</v>
+      </c>
+      <c r="F324" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="325" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>166</v>
       </c>
@@ -6107,13 +6170,442 @@
       <c r="D325" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="326" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E325" t="s">
+        <v>168</v>
+      </c>
+      <c r="F325" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="326" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>166</v>
       </c>
       <c r="B326" t="s">
         <v>164</v>
+      </c>
+      <c r="E326" t="s">
+        <v>168</v>
+      </c>
+      <c r="F326" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="329" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B329" t="s">
+        <v>292</v>
+      </c>
+      <c r="D329" t="s">
+        <v>297</v>
+      </c>
+      <c r="F329" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="330" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A330" t="s">
+        <v>99</v>
+      </c>
+      <c r="B330" t="s">
+        <v>235</v>
+      </c>
+      <c r="C330" t="s">
+        <v>101</v>
+      </c>
+      <c r="D330" t="s">
+        <v>244</v>
+      </c>
+      <c r="E330" t="s">
+        <v>101</v>
+      </c>
+      <c r="F330" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="331" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A331" t="s">
+        <v>101</v>
+      </c>
+      <c r="B331" t="s">
+        <v>64</v>
+      </c>
+      <c r="C331" t="s">
+        <v>101</v>
+      </c>
+      <c r="D331" t="s">
+        <v>68</v>
+      </c>
+      <c r="E331" t="s">
+        <v>101</v>
+      </c>
+      <c r="F331" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="332" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A332" t="s">
+        <v>99</v>
+      </c>
+      <c r="B332" t="s">
+        <v>154</v>
+      </c>
+      <c r="C332" t="s">
+        <v>101</v>
+      </c>
+      <c r="D332" t="s">
+        <v>242</v>
+      </c>
+      <c r="E332" t="s">
+        <v>99</v>
+      </c>
+      <c r="F332" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="334" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A334" t="s">
+        <v>101</v>
+      </c>
+      <c r="B334" t="s">
+        <v>63</v>
+      </c>
+      <c r="C334" t="s">
+        <v>91</v>
+      </c>
+      <c r="D334" t="s">
+        <v>198</v>
+      </c>
+      <c r="E334" t="s">
+        <v>155</v>
+      </c>
+      <c r="F334" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="335" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A335" t="s">
+        <v>101</v>
+      </c>
+      <c r="B335" t="s">
+        <v>246</v>
+      </c>
+      <c r="C335" t="s">
+        <v>91</v>
+      </c>
+      <c r="D335" t="s">
+        <v>206</v>
+      </c>
+      <c r="E335" t="s">
+        <v>91</v>
+      </c>
+      <c r="F335" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="336" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A336" t="s">
+        <v>101</v>
+      </c>
+      <c r="B336" t="s">
+        <v>237</v>
+      </c>
+      <c r="C336" t="s">
+        <v>91</v>
+      </c>
+      <c r="D336" t="s">
+        <v>273</v>
+      </c>
+      <c r="E336" t="s">
+        <v>155</v>
+      </c>
+      <c r="F336" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="338" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A338" t="s">
+        <v>93</v>
+      </c>
+      <c r="B338" t="s">
+        <v>19</v>
+      </c>
+      <c r="C338" t="s">
+        <v>93</v>
+      </c>
+      <c r="D338" t="s">
+        <v>295</v>
+      </c>
+      <c r="E338" t="s">
+        <v>93</v>
+      </c>
+      <c r="F338" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="340" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A340" t="s">
+        <v>101</v>
+      </c>
+      <c r="B340" t="s">
+        <v>294</v>
+      </c>
+      <c r="C340" t="s">
+        <v>101</v>
+      </c>
+      <c r="D340" t="s">
+        <v>296</v>
+      </c>
+      <c r="E340" t="s">
+        <v>101</v>
+      </c>
+      <c r="F340" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="341" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A341" t="s">
+        <v>84</v>
+      </c>
+      <c r="B341" t="s">
+        <v>293</v>
+      </c>
+      <c r="C341" t="s">
+        <v>99</v>
+      </c>
+      <c r="D341" t="s">
+        <v>81</v>
+      </c>
+      <c r="E341" t="s">
+        <v>101</v>
+      </c>
+      <c r="F341" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="343" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A343" t="s">
+        <v>211</v>
+      </c>
+      <c r="B343" t="s">
+        <v>61</v>
+      </c>
+      <c r="C343" t="s">
+        <v>99</v>
+      </c>
+      <c r="D343" t="s">
+        <v>66</v>
+      </c>
+      <c r="E343" t="s">
+        <v>101</v>
+      </c>
+      <c r="F343" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="344" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A344" t="s">
+        <v>99</v>
+      </c>
+      <c r="B344" t="s">
+        <v>150</v>
+      </c>
+      <c r="C344" t="s">
+        <v>99</v>
+      </c>
+      <c r="D344" t="s">
+        <v>54</v>
+      </c>
+      <c r="E344" t="s">
+        <v>101</v>
+      </c>
+      <c r="F344" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="345" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C345" t="s">
+        <v>99</v>
+      </c>
+      <c r="D345" t="s">
+        <v>163</v>
+      </c>
+      <c r="E345" t="s">
+        <v>127</v>
+      </c>
+      <c r="F345" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="347" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B347" t="s">
+        <v>252</v>
+      </c>
+      <c r="D347" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="348" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A348" t="s">
+        <v>101</v>
+      </c>
+      <c r="B348" t="s">
+        <v>255</v>
+      </c>
+      <c r="C348" t="s">
+        <v>101</v>
+      </c>
+      <c r="D348" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="349" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A349" t="s">
+        <v>101</v>
+      </c>
+      <c r="B349" t="s">
+        <v>39</v>
+      </c>
+      <c r="C349" t="s">
+        <v>101</v>
+      </c>
+      <c r="D349" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="350" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A350" t="s">
+        <v>99</v>
+      </c>
+      <c r="B350" t="s">
+        <v>55</v>
+      </c>
+      <c r="C350" t="s">
+        <v>211</v>
+      </c>
+      <c r="D350" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="352" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A352" t="s">
+        <v>91</v>
+      </c>
+      <c r="B352" t="s">
+        <v>253</v>
+      </c>
+      <c r="C352" t="s">
+        <v>91</v>
+      </c>
+      <c r="D352" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="353" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A353" t="s">
+        <v>91</v>
+      </c>
+      <c r="B353" t="s">
+        <v>40</v>
+      </c>
+      <c r="C353" t="s">
+        <v>91</v>
+      </c>
+      <c r="D353" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="354" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A354" t="s">
+        <v>91</v>
+      </c>
+      <c r="B354" t="s">
+        <v>258</v>
+      </c>
+      <c r="C354" t="s">
+        <v>91</v>
+      </c>
+      <c r="D354" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="356" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A356" t="s">
+        <v>101</v>
+      </c>
+      <c r="B356" t="s">
+        <v>256</v>
+      </c>
+      <c r="C356" t="s">
+        <v>93</v>
+      </c>
+      <c r="D356" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="357" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A357" t="s">
+        <v>101</v>
+      </c>
+      <c r="B357" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="358" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A358" t="s">
+        <v>101</v>
+      </c>
+      <c r="B358" t="s">
+        <v>33</v>
+      </c>
+      <c r="C358" t="s">
+        <v>101</v>
+      </c>
+      <c r="D358" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="359" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C359" t="s">
+        <v>99</v>
+      </c>
+      <c r="D359" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="360" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A360" t="s">
+        <v>101</v>
+      </c>
+      <c r="B360" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="361" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A361" t="s">
+        <v>101</v>
+      </c>
+      <c r="B361" t="s">
+        <v>124</v>
+      </c>
+      <c r="C361" t="s">
+        <v>101</v>
+      </c>
+      <c r="D361" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="362" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A362" t="s">
+        <v>168</v>
+      </c>
+      <c r="B362" t="s">
+        <v>228</v>
+      </c>
+      <c r="C362" t="s">
+        <v>99</v>
+      </c>
+      <c r="D362" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/docs/wo.xlsx
+++ b/docs/wo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\milne\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nmilner\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBC733CE-D42D-4BC6-BF5B-1781D3A90779}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6360407-A539-4FAE-97F4-E847F7D0DF7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{C32645C5-10AA-4D5C-BF11-217FF2F37ECD}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{C32645C5-10AA-4D5C-BF11-217FF2F37ECD}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1515" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1538" uniqueCount="315">
   <si>
     <t>Pause Barbell Lunge</t>
   </si>
@@ -979,6 +979,9 @@
   </si>
   <si>
     <t>DB RDL to Shrug</t>
+  </si>
+  <si>
+    <t>Pull-Ups</t>
   </si>
 </sst>
 </file>
@@ -6443,6 +6446,9 @@
       <c r="D347" t="s">
         <v>254</v>
       </c>
+      <c r="F347" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
@@ -6457,6 +6463,12 @@
       <c r="D348" t="s">
         <v>260</v>
       </c>
+      <c r="E348" t="s">
+        <v>101</v>
+      </c>
+      <c r="F348" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="349" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
@@ -6466,10 +6478,16 @@
         <v>39</v>
       </c>
       <c r="C349" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="D349" t="s">
-        <v>306</v>
+        <v>314</v>
+      </c>
+      <c r="E349" t="s">
+        <v>101</v>
+      </c>
+      <c r="F349" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.25">
@@ -6485,6 +6503,12 @@
       <c r="D350" t="s">
         <v>190</v>
       </c>
+      <c r="E350" t="s">
+        <v>101</v>
+      </c>
+      <c r="F350" t="s">
+        <v>310</v>
+      </c>
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
@@ -6499,8 +6523,14 @@
       <c r="D352" t="s">
         <v>263</v>
       </c>
-    </row>
-    <row r="353" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E352" t="s">
+        <v>91</v>
+      </c>
+      <c r="F352" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="353" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>91</v>
       </c>
@@ -6511,10 +6541,16 @@
         <v>91</v>
       </c>
       <c r="D353" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="354" spans="1:4" x14ac:dyDescent="0.25">
+        <v>162</v>
+      </c>
+      <c r="E353" t="s">
+        <v>91</v>
+      </c>
+      <c r="F353" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="354" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>91</v>
       </c>
@@ -6525,10 +6561,16 @@
         <v>91</v>
       </c>
       <c r="D354" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="356" spans="1:4" x14ac:dyDescent="0.25">
+        <v>299</v>
+      </c>
+      <c r="E354" t="s">
+        <v>91</v>
+      </c>
+      <c r="F354" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="356" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>101</v>
       </c>
@@ -6541,8 +6583,14 @@
       <c r="D356" t="s">
         <v>273</v>
       </c>
-    </row>
-    <row r="357" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E356" t="s">
+        <v>93</v>
+      </c>
+      <c r="F356" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="357" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>101</v>
       </c>
@@ -6550,7 +6598,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="358" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>101</v>
       </c>
@@ -6563,16 +6611,28 @@
       <c r="D358" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="359" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E358" t="s">
+        <v>99</v>
+      </c>
+      <c r="F358" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="359" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C359" t="s">
         <v>99</v>
       </c>
       <c r="D359" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="360" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E359" t="s">
+        <v>101</v>
+      </c>
+      <c r="F359" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="360" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>101</v>
       </c>
@@ -6580,7 +6640,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="361" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>101</v>
       </c>
@@ -6593,8 +6653,14 @@
       <c r="D361" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="362" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E361" t="s">
+        <v>99</v>
+      </c>
+      <c r="F361" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="362" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
         <v>168</v>
       </c>
@@ -6606,6 +6672,12 @@
       </c>
       <c r="D362" t="s">
         <v>44</v>
+      </c>
+      <c r="E362" t="s">
+        <v>99</v>
+      </c>
+      <c r="F362" t="s">
+        <v>268</v>
       </c>
     </row>
   </sheetData>

--- a/docs/wo.xlsx
+++ b/docs/wo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nmilner\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\milne\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6360407-A539-4FAE-97F4-E847F7D0DF7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8AB1C59-7957-451E-82FA-57DADFC5622C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{C32645C5-10AA-4D5C-BF11-217FF2F37ECD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{C32645C5-10AA-4D5C-BF11-217FF2F37ECD}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1538" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1651" uniqueCount="315">
   <si>
     <t>Pause Barbell Lunge</t>
   </si>
@@ -981,7 +981,7 @@
     <t>DB RDL to Shrug</t>
   </si>
   <si>
-    <t>Pull-Ups</t>
+    <t>Face pulls</t>
   </si>
 </sst>
 </file>
@@ -1891,7 +1891,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A791CA79-5EDF-4534-95D3-2767A2C8696F}">
-  <dimension ref="A2:S362"/>
+  <dimension ref="A2:S397"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.7109375" customWidth="1"/>
@@ -6478,10 +6478,10 @@
         <v>39</v>
       </c>
       <c r="C349" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
       <c r="D349" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="E349" t="s">
         <v>101</v>
@@ -6541,7 +6541,7 @@
         <v>91</v>
       </c>
       <c r="D353" t="s">
-        <v>162</v>
+        <v>19</v>
       </c>
       <c r="E353" t="s">
         <v>91</v>
@@ -6561,7 +6561,7 @@
         <v>91</v>
       </c>
       <c r="D354" t="s">
-        <v>299</v>
+        <v>262</v>
       </c>
       <c r="E354" t="s">
         <v>91</v>
@@ -6678,6 +6678,395 @@
       </c>
       <c r="F362" t="s">
         <v>268</v>
+      </c>
+    </row>
+    <row r="365" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B365" t="s">
+        <v>269</v>
+      </c>
+      <c r="D365" t="s">
+        <v>272</v>
+      </c>
+      <c r="F365" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="366" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A366" t="s">
+        <v>101</v>
+      </c>
+      <c r="B366" t="s">
+        <v>235</v>
+      </c>
+      <c r="C366" t="s">
+        <v>101</v>
+      </c>
+      <c r="D366" t="s">
+        <v>227</v>
+      </c>
+      <c r="E366" t="s">
+        <v>99</v>
+      </c>
+      <c r="F366" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="367" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A367" t="s">
+        <v>101</v>
+      </c>
+      <c r="B367" t="s">
+        <v>121</v>
+      </c>
+      <c r="C367" t="s">
+        <v>101</v>
+      </c>
+      <c r="D367" t="s">
+        <v>274</v>
+      </c>
+      <c r="E367" t="s">
+        <v>99</v>
+      </c>
+      <c r="F367" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="368" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A368" t="s">
+        <v>99</v>
+      </c>
+      <c r="B368" t="s">
+        <v>313</v>
+      </c>
+      <c r="C368" t="s">
+        <v>99</v>
+      </c>
+      <c r="D368" t="s">
+        <v>239</v>
+      </c>
+      <c r="E368" t="s">
+        <v>99</v>
+      </c>
+      <c r="F368" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="370" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A370" t="s">
+        <v>91</v>
+      </c>
+      <c r="B370" t="s">
+        <v>9</v>
+      </c>
+      <c r="C370" t="s">
+        <v>91</v>
+      </c>
+      <c r="D370" t="s">
+        <v>273</v>
+      </c>
+      <c r="E370" t="s">
+        <v>91</v>
+      </c>
+      <c r="F370" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="371" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A371" t="s">
+        <v>91</v>
+      </c>
+      <c r="B371" t="s">
+        <v>30</v>
+      </c>
+      <c r="C371" t="s">
+        <v>155</v>
+      </c>
+      <c r="D371" t="s">
+        <v>55</v>
+      </c>
+      <c r="E371" t="s">
+        <v>91</v>
+      </c>
+      <c r="F371" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="372" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A372" t="s">
+        <v>91</v>
+      </c>
+      <c r="B372" t="s">
+        <v>202</v>
+      </c>
+      <c r="C372" t="s">
+        <v>114</v>
+      </c>
+      <c r="D372" t="s">
+        <v>115</v>
+      </c>
+      <c r="E372" t="s">
+        <v>155</v>
+      </c>
+      <c r="F372" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="374" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A374" t="s">
+        <v>93</v>
+      </c>
+      <c r="B374" t="s">
+        <v>246</v>
+      </c>
+      <c r="C374" t="s">
+        <v>277</v>
+      </c>
+      <c r="D374" t="s">
+        <v>276</v>
+      </c>
+      <c r="E374" t="s">
+        <v>93</v>
+      </c>
+      <c r="F374" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="375" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C375" t="s">
+        <v>101</v>
+      </c>
+      <c r="D375" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="376" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A376" t="s">
+        <v>101</v>
+      </c>
+      <c r="B376" t="s">
+        <v>288</v>
+      </c>
+      <c r="C376" t="s">
+        <v>99</v>
+      </c>
+      <c r="D376" t="s">
+        <v>159</v>
+      </c>
+      <c r="E376" t="s">
+        <v>99</v>
+      </c>
+      <c r="F376" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="378" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A378" t="s">
+        <v>168</v>
+      </c>
+      <c r="B378" t="s">
+        <v>228</v>
+      </c>
+      <c r="C378" t="s">
+        <v>211</v>
+      </c>
+      <c r="D378" t="s">
+        <v>61</v>
+      </c>
+      <c r="E378" t="s">
+        <v>84</v>
+      </c>
+      <c r="F378" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="379" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A379" t="s">
+        <v>166</v>
+      </c>
+      <c r="B379" t="s">
+        <v>180</v>
+      </c>
+      <c r="C379" t="s">
+        <v>99</v>
+      </c>
+      <c r="D379" t="s">
+        <v>150</v>
+      </c>
+      <c r="E379" t="s">
+        <v>99</v>
+      </c>
+      <c r="F379" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="380" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A380" t="s">
+        <v>99</v>
+      </c>
+      <c r="B380" t="s">
+        <v>163</v>
+      </c>
+      <c r="E380" t="s">
+        <v>101</v>
+      </c>
+      <c r="F380" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="382" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B382" t="s">
+        <v>283</v>
+      </c>
+      <c r="D382" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="383" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A383" t="s">
+        <v>101</v>
+      </c>
+      <c r="B383" t="s">
+        <v>182</v>
+      </c>
+      <c r="C383" t="s">
+        <v>99</v>
+      </c>
+      <c r="D383" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="384" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A384" t="s">
+        <v>101</v>
+      </c>
+      <c r="B384" t="s">
+        <v>286</v>
+      </c>
+      <c r="C384" t="s">
+        <v>101</v>
+      </c>
+      <c r="D384" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="385" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A385" t="s">
+        <v>84</v>
+      </c>
+      <c r="B385" t="s">
+        <v>285</v>
+      </c>
+      <c r="C385" t="s">
+        <v>101</v>
+      </c>
+      <c r="D385" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="387" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A387" t="s">
+        <v>91</v>
+      </c>
+      <c r="B387" t="s">
+        <v>284</v>
+      </c>
+      <c r="C387" t="s">
+        <v>91</v>
+      </c>
+      <c r="D387" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="388" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A388" t="s">
+        <v>91</v>
+      </c>
+      <c r="B388" t="s">
+        <v>39</v>
+      </c>
+      <c r="C388" t="s">
+        <v>91</v>
+      </c>
+      <c r="D388" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="389" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A389" t="s">
+        <v>91</v>
+      </c>
+      <c r="B389" t="s">
+        <v>27</v>
+      </c>
+      <c r="C389" t="s">
+        <v>91</v>
+      </c>
+      <c r="D389" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="391" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A391" t="s">
+        <v>93</v>
+      </c>
+      <c r="B391" t="s">
+        <v>30</v>
+      </c>
+      <c r="C391" t="s">
+        <v>93</v>
+      </c>
+      <c r="D391" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="393" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A393" t="s">
+        <v>99</v>
+      </c>
+      <c r="B393" t="s">
+        <v>157</v>
+      </c>
+      <c r="C393" t="s">
+        <v>101</v>
+      </c>
+      <c r="D393" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="395" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A395" t="s">
+        <v>99</v>
+      </c>
+      <c r="B395" t="s">
+        <v>163</v>
+      </c>
+      <c r="C395" t="s">
+        <v>101</v>
+      </c>
+      <c r="D395" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="396" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A396" t="s">
+        <v>166</v>
+      </c>
+      <c r="B396" t="s">
+        <v>165</v>
+      </c>
+      <c r="C396" t="s">
+        <v>99</v>
+      </c>
+      <c r="D396" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="397" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A397" t="s">
+        <v>166</v>
+      </c>
+      <c r="B397" t="s">
+        <v>164</v>
       </c>
     </row>
   </sheetData>

--- a/docs/wo.xlsx
+++ b/docs/wo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\milne\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8AB1C59-7957-451E-82FA-57DADFC5622C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72296DC3-53BB-43A2-BADB-709D732C8399}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{C32645C5-10AA-4D5C-BF11-217FF2F37ECD}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1651" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1718" uniqueCount="315">
   <si>
     <t>Pause Barbell Lunge</t>
   </si>
@@ -1891,7 +1891,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A791CA79-5EDF-4534-95D3-2767A2C8696F}">
-  <dimension ref="A2:S397"/>
+  <dimension ref="A2:S415"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.7109375" customWidth="1"/>
@@ -6920,6 +6920,9 @@
       <c r="D382" t="s">
         <v>287</v>
       </c>
+      <c r="F382" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="383" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
@@ -6934,6 +6937,12 @@
       <c r="D383" t="s">
         <v>314</v>
       </c>
+      <c r="E383" t="s">
+        <v>101</v>
+      </c>
+      <c r="F383" t="s">
+        <v>303</v>
+      </c>
     </row>
     <row r="384" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
@@ -6948,8 +6957,14 @@
       <c r="D384" t="s">
         <v>290</v>
       </c>
-    </row>
-    <row r="385" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E384" t="s">
+        <v>101</v>
+      </c>
+      <c r="F384" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="385" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
         <v>84</v>
       </c>
@@ -6962,8 +6977,14 @@
       <c r="D385" t="s">
         <v>288</v>
       </c>
-    </row>
-    <row r="387" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E385" t="s">
+        <v>99</v>
+      </c>
+      <c r="F385" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="387" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
         <v>91</v>
       </c>
@@ -6976,8 +6997,14 @@
       <c r="D387" t="s">
         <v>271</v>
       </c>
-    </row>
-    <row r="388" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E387" t="s">
+        <v>101</v>
+      </c>
+      <c r="F387" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="388" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
         <v>91</v>
       </c>
@@ -6990,8 +7017,14 @@
       <c r="D388" t="s">
         <v>260</v>
       </c>
-    </row>
-    <row r="389" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E388" t="s">
+        <v>101</v>
+      </c>
+      <c r="F388" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="389" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
         <v>91</v>
       </c>
@@ -7004,8 +7037,14 @@
       <c r="D389" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="391" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E389" t="s">
+        <v>99</v>
+      </c>
+      <c r="F389" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="391" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
         <v>93</v>
       </c>
@@ -7018,8 +7057,14 @@
       <c r="D391" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="393" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E391" t="s">
+        <v>93</v>
+      </c>
+      <c r="F391" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="393" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
         <v>99</v>
       </c>
@@ -7032,8 +7077,14 @@
       <c r="D393" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="395" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E393" t="s">
+        <v>99</v>
+      </c>
+      <c r="F393" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="395" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
         <v>99</v>
       </c>
@@ -7046,8 +7097,14 @@
       <c r="D395" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="396" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E395" t="s">
+        <v>168</v>
+      </c>
+      <c r="F395" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="396" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
         <v>166</v>
       </c>
@@ -7060,13 +7117,181 @@
       <c r="D396" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="397" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E396" t="s">
+        <v>168</v>
+      </c>
+      <c r="F396" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="397" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
         <v>166</v>
       </c>
       <c r="B397" t="s">
         <v>164</v>
+      </c>
+      <c r="E397" t="s">
+        <v>168</v>
+      </c>
+      <c r="F397" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="400" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B400" t="s">
+        <v>292</v>
+      </c>
+      <c r="D400" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="401" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A401" t="s">
+        <v>99</v>
+      </c>
+      <c r="B401" t="s">
+        <v>235</v>
+      </c>
+      <c r="C401" t="s">
+        <v>101</v>
+      </c>
+      <c r="D401" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="402" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A402" t="s">
+        <v>101</v>
+      </c>
+      <c r="B402" t="s">
+        <v>64</v>
+      </c>
+      <c r="C402" t="s">
+        <v>101</v>
+      </c>
+      <c r="D402" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="403" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A403" t="s">
+        <v>99</v>
+      </c>
+      <c r="B403" t="s">
+        <v>154</v>
+      </c>
+      <c r="C403" t="s">
+        <v>101</v>
+      </c>
+      <c r="D403" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="405" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A405" t="s">
+        <v>101</v>
+      </c>
+      <c r="B405" t="s">
+        <v>63</v>
+      </c>
+      <c r="C405" t="s">
+        <v>101</v>
+      </c>
+      <c r="D405" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="406" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A406" t="s">
+        <v>101</v>
+      </c>
+      <c r="B406" t="s">
+        <v>246</v>
+      </c>
+      <c r="C406" t="s">
+        <v>101</v>
+      </c>
+      <c r="D406" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="407" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A407" t="s">
+        <v>101</v>
+      </c>
+      <c r="B407" t="s">
+        <v>237</v>
+      </c>
+      <c r="C407" t="s">
+        <v>101</v>
+      </c>
+      <c r="D407" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="409" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A409" t="s">
+        <v>93</v>
+      </c>
+      <c r="B409" t="s">
+        <v>19</v>
+      </c>
+      <c r="C409" t="s">
+        <v>93</v>
+      </c>
+      <c r="D409" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="411" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A411" t="s">
+        <v>101</v>
+      </c>
+      <c r="B411" t="s">
+        <v>294</v>
+      </c>
+      <c r="C411" t="s">
+        <v>99</v>
+      </c>
+      <c r="D411" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="413" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A413" t="s">
+        <v>211</v>
+      </c>
+      <c r="B413" t="s">
+        <v>61</v>
+      </c>
+      <c r="C413" t="s">
+        <v>99</v>
+      </c>
+      <c r="D413" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="414" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A414" t="s">
+        <v>99</v>
+      </c>
+      <c r="B414" t="s">
+        <v>150</v>
+      </c>
+      <c r="C414" t="s">
+        <v>99</v>
+      </c>
+      <c r="D414" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="415" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C415" t="s">
+        <v>99</v>
+      </c>
+      <c r="D415" t="s">
+        <v>163</v>
       </c>
     </row>
   </sheetData>
